--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -555,6 +555,63 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1320-600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCHER C COTINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Sto. Nino, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1347-156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHARLO F  SALUMAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/a, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1363-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLAUDIO  E. ELNAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1348-671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWIN M SAGAYNO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SROPIX-16152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1349-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAMON M SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SROPIX-16133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1350-437</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1504,56 +1561,251 @@
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="27" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D8" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="27" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F8" s="27" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G8" s="27" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H8" s="29">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I8" s="30">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J8" s="28" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="32">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M8" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="27" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="27" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F9" s="27" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G9" s="27" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H9" s="29">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I9" s="30">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J9" s="28" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="32">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M9" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I10" s="30">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J10" s="28" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K10" s="31" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L10" s="32">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I11" s="30">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J11" s="28" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K11" s="31" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="32">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J12" s="28" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L12" s="32">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
+      <x:c r="C15" s="16" t="s"/>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="17" t="s"/>
+      <x:c r="F15" s="17" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="18" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="21" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
-        <x:v>2</x:v>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2529,13 +2781,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -603,6 +603,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1349-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PONCIANO O. SINDAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Samboang, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ponciano O. Sinday</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1365-581</x:t>
   </x:si>
   <x:si>
     <x:t>RAMON M SILVA</x:t>
@@ -1724,89 +1736,126 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="27" t="s">
-        <x:v>188</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F12" s="27" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G12" s="27" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="29">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M12" s="27" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L13" s="32">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="s"/>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="17" t="s"/>
-      <x:c r="F15" s="17" t="s"/>
+      <x:c r="C16" s="16" t="s"/>
+      <x:c r="D16" s="16" t="s"/>
+      <x:c r="E16" s="17" t="s"/>
+      <x:c r="F16" s="17" t="s"/>
     </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="18" t="s">
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="18" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="20" t="s">
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="19" t="s"/>
+      <x:c r="F17" s="20" t="s">
         <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="22" t="s"/>
       <x:c r="D18" s="22" t="s"/>
       <x:c r="E18" s="22" t="s"/>
       <x:c r="F18" s="23" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="24" t="s">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
-        <x:v>7</x:v>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2784,11 +2833,11 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -555,6 +555,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1320-600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTURO D ANTONIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, San Carlos, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17-SROPIX-11057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
     <x:t>ARCHER C COTINA</x:t>
@@ -1575,7 +1587,7 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C8" s="27" t="s">
         <x:v>175</x:v>
@@ -1593,19 +1605,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="29">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46072.3153009259</x:v>
       </x:c>
       <x:c r="I8" s="30">
-        <x:v>46042</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J8" s="28" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216162</x:v>
       </x:c>
       <x:c r="K8" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L8" s="32">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.311412037</x:v>
       </x:c>
       <x:c r="M8" s="27" t="s">
         <x:v>19</x:v>
@@ -1631,19 +1643,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H9" s="29">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I9" s="30">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J9" s="28" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K9" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M9" s="27" t="s">
         <x:v>19</x:v>
@@ -1669,19 +1681,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H10" s="29">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I10" s="30">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J10" s="28" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M10" s="27" t="s">
         <x:v>19</x:v>
@@ -1707,19 +1719,19 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H11" s="29">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J11" s="28" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M11" s="27" t="s">
         <x:v>19</x:v>
@@ -1745,19 +1757,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="29">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>45748</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M12" s="27" t="s">
         <x:v>19</x:v>
@@ -1774,90 +1786,137 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="27" t="s">
-        <x:v>188</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F13" s="27" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G13" s="27" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H13" s="29">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J13" s="28" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M13" s="27" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I14" s="30">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J14" s="28" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L14" s="32">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="s"/>
-      <x:c r="D16" s="16" t="s"/>
-      <x:c r="E16" s="17" t="s"/>
-      <x:c r="F16" s="17" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="18" t="s">
+      <x:c r="C17" s="16" t="s"/>
+      <x:c r="D17" s="16" t="s"/>
+      <x:c r="E17" s="17" t="s"/>
+      <x:c r="F17" s="17" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="18" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="19" t="s"/>
-      <x:c r="F17" s="20" t="s">
+      <x:c r="C18" s="19" t="s"/>
+      <x:c r="D18" s="19" t="s"/>
+      <x:c r="E18" s="19" t="s"/>
+      <x:c r="F18" s="20" t="s">
         <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="22" t="s"/>
       <x:c r="D19" s="22" t="s"/>
       <x:c r="E19" s="22" t="s"/>
       <x:c r="F19" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2830,14 +2889,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -605,12 +605,21 @@
     <x:t>61-2-2026-1348-671</x:t>
   </x:si>
   <x:si>
+    <x:t>EDGAR S SERENCIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24-SROPIX-16132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1351-693</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN M SAGAYNO</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
     <x:t>-SROPIX-16152</x:t>
   </x:si>
   <x:si>
@@ -636,6 +645,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1350-437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBERTO Q CORPIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Limamawan, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1361-291</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1757,19 +1778,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="29">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46036</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M12" s="27" t="s">
         <x:v>19</x:v>
@@ -1786,28 +1807,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="G13" s="27" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
-        <x:v>198</x:v>
-      </x:c>
       <x:c r="H13" s="29">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>45748</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J13" s="28" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M13" s="27" t="s">
         <x:v>19</x:v>
@@ -1818,13 +1839,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D14" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="27" t="s">
-        <x:v>192</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F14" s="27" t="s">
         <x:v>200</x:v>
@@ -1833,92 +1854,166 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H14" s="29">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J14" s="28" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M14" s="27" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F15" s="27" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H15" s="29">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L15" s="32">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M15" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H16" s="29">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J16" s="28" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L16" s="32">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M16" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C17" s="16" t="s"/>
-      <x:c r="D17" s="16" t="s"/>
-      <x:c r="E17" s="17" t="s"/>
-      <x:c r="F17" s="17" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="18" t="s">
+      <x:c r="C19" s="16" t="s"/>
+      <x:c r="D19" s="16" t="s"/>
+      <x:c r="E19" s="17" t="s"/>
+      <x:c r="F19" s="17" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="18" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C18" s="19" t="s"/>
-      <x:c r="D18" s="19" t="s"/>
-      <x:c r="E18" s="19" t="s"/>
-      <x:c r="F18" s="20" t="s">
+      <x:c r="C20" s="19" t="s"/>
+      <x:c r="D20" s="19" t="s"/>
+      <x:c r="E20" s="19" t="s"/>
+      <x:c r="F20" s="20" t="s">
         <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C21" s="22" t="s"/>
       <x:c r="D21" s="22" t="s"/>
       <x:c r="E21" s="22" t="s"/>
       <x:c r="F21" s="23" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="22" t="s"/>
+      <x:c r="F22" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="s"/>
+      <x:c r="D23" s="22" t="s"/>
+      <x:c r="E23" s="22" t="s"/>
+      <x:c r="F23" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="n">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2892,12 +2987,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -545,6 +545,18 @@
     <x:t>61-2-2026-1322-666</x:t>
   </x:si>
   <x:si>
+    <x:t>LILIA R. FLORIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK 1, BINTANA, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97-1PX-18986</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1378-820</x:t>
+  </x:si>
+  <x:si>
     <x:t>MERIAM MANON-OG LICAYAN</x:t>
   </x:si>
   <x:si>
@@ -555,6 +567,30 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1320-600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MYRNA M MANUGAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A P-6, Lorenzo, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-3PX-3945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1381-306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WILMA E BERMUDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Saging-saging, Micanaway, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-1PX-23569</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1379-115</x:t>
   </x:si>
   <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
@@ -1587,19 +1623,19 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46065.2288541667</x:v>
+        <x:v>46085.2764814815</x:v>
       </x:c>
       <x:c r="I7" s="13">
-        <x:v>46070</x:v>
+        <x:v>44879</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216140</x:v>
+        <x:v>1216175</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
-        <x:v>390</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46084.1582175926</x:v>
+        <x:v>46093.2000115741</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>19</x:v>
@@ -1608,7 +1644,7 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="27" t="s">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="27" t="s">
         <x:v>175</x:v>
@@ -1626,19 +1662,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="29">
-        <x:v>46072.3153009259</x:v>
+        <x:v>46065.2288541667</x:v>
       </x:c>
       <x:c r="I8" s="30">
-        <x:v>46114</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J8" s="28" t="n">
-        <x:v>1216162</x:v>
+        <x:v>1216140</x:v>
       </x:c>
       <x:c r="K8" s="31" t="n">
-        <x:v>270</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L8" s="32">
-        <x:v>46090.311412037</x:v>
+        <x:v>46084.1582175926</x:v>
       </x:c>
       <x:c r="M8" s="27" t="s">
         <x:v>19</x:v>
@@ -1646,7 +1682,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="27" t="s">
         <x:v>179</x:v>
@@ -1664,19 +1700,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H9" s="29">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46085.3007986111</x:v>
       </x:c>
       <x:c r="I9" s="30">
-        <x:v>46042</x:v>
+        <x:v>46386</x:v>
       </x:c>
       <x:c r="J9" s="28" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216177</x:v>
       </x:c>
       <x:c r="K9" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46090.267025463</x:v>
+        <x:v>46093.215162037</x:v>
       </x:c>
       <x:c r="M9" s="27" t="s">
         <x:v>19</x:v>
@@ -1684,7 +1720,7 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="27" t="s">
         <x:v>183</x:v>
@@ -1702,19 +1738,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H10" s="29">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46085.2858333333</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46042</x:v>
+        <x:v>46096</x:v>
       </x:c>
       <x:c r="J10" s="28" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216176</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46093.2057060185</x:v>
       </x:c>
       <x:c r="M10" s="27" t="s">
         <x:v>19</x:v>
@@ -1722,7 +1758,7 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C11" s="27" t="s">
         <x:v>187</x:v>
@@ -1740,19 +1776,19 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H11" s="29">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46072.3153009259</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46042</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J11" s="28" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216162</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.311412037</x:v>
       </x:c>
       <x:c r="M11" s="27" t="s">
         <x:v>19</x:v>
@@ -1778,19 +1814,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="29">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M12" s="27" t="s">
         <x:v>19</x:v>
@@ -1807,28 +1843,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="27" t="s">
-        <x:v>192</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F13" s="27" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G13" s="27" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H13" s="29">
-        <x:v>46073.061099537</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J13" s="28" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M13" s="27" t="s">
         <x:v>19</x:v>
@@ -1839,34 +1875,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D14" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="27" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F14" s="27" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G14" s="27" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H14" s="29">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J14" s="28" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M14" s="27" t="s">
         <x:v>19</x:v>
@@ -1877,34 +1913,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="27" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D15" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="27" t="s">
-        <x:v>192</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F15" s="27" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G15" s="27" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H15" s="29">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I15" s="30">
         <x:v>45824</x:v>
       </x:c>
       <x:c r="J15" s="28" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M15" s="27" t="s">
         <x:v>19</x:v>
@@ -1915,108 +1951,219 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D16" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="27" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F16" s="27" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G16" s="27" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H16" s="29">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46115</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J16" s="28" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M16" s="27" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="27" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F17" s="27" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H17" s="29">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J17" s="28" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K17" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L17" s="32">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M17" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F18" s="27" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H18" s="29">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J18" s="28" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K18" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L18" s="32">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M18" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D19" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="27" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F19" s="27" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G19" s="27" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H19" s="29">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J19" s="28" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L19" s="32">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M19" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C19" s="16" t="s"/>
-      <x:c r="D19" s="16" t="s"/>
-      <x:c r="E19" s="17" t="s"/>
-      <x:c r="F19" s="17" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="18" t="s">
+      <x:c r="C22" s="16" t="s"/>
+      <x:c r="D22" s="16" t="s"/>
+      <x:c r="E22" s="17" t="s"/>
+      <x:c r="F22" s="17" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="18" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C20" s="19" t="s"/>
-      <x:c r="D20" s="19" t="s"/>
-      <x:c r="E20" s="19" t="s"/>
-      <x:c r="F20" s="20" t="s">
+      <x:c r="C23" s="19" t="s"/>
+      <x:c r="D23" s="19" t="s"/>
+      <x:c r="E23" s="19" t="s"/>
+      <x:c r="F23" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="21" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="21" t="s">
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="22" t="s"/>
+      <x:c r="F24" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="21" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="n">
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="21" t="s">
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="23" t="n">
+      <x:c r="C26" s="22" t="s"/>
+      <x:c r="D26" s="22" t="s"/>
+      <x:c r="E26" s="22" t="s"/>
+      <x:c r="F26" s="23" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="24" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2987,12 +3134,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B22:F22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -362,7 +362,7 @@
     <x:t>61-11-2025-1227</x:t>
   </x:si>
   <x:si>
-    <x:t>RUEL  BUGAS BALILI</x:t>
+    <x:t>RUEL BUGAS BALILI</x:t>
   </x:si>
   <x:si>
     <x:t>24-SROPPIX-16142</x:t>
@@ -617,7 +617,7 @@
     <x:t>61-2-2026-1347-156</x:t>
   </x:si>
   <x:si>
-    <x:t>CHARLO F  SALUMAG</x:t>
+    <x:t>CHARLO F SALUMAG</x:t>
   </x:si>
   <x:si>
     <x:t>N/A N/a, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
@@ -629,7 +629,7 @@
     <x:t>61-2-2026-1363-573</x:t>
   </x:si>
   <x:si>
-    <x:t>CLAUDIO  E. ELNAR</x:t>
+    <x:t>CLAUDIO E. ELNAR</x:t>
   </x:si>
   <x:si>
     <x:t>N/a N/A, Poblacion, Tukuran, Zamboanga Del Sur</x:t>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -693,6 +693,30 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1361-291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODEL PALMERO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 4, GUIPOS, Guipos, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17SROPIX11062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1336-018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROMEO CAPANGPANGAN DUMAOG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NA GUMAMELA, SAN CARLOS, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22-SROPIX-13860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1390-540</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2098,74 +2122,148 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D20" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="27" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F20" s="27" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G20" s="27" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H20" s="29">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I20" s="30">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J20" s="28" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K20" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="32">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M20" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D21" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="27" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F21" s="27" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G21" s="27" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H21" s="29">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J21" s="28" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K21" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L21" s="32">
+        <x:v>46094.182662037</x:v>
+      </x:c>
+      <x:c r="M21" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C22" s="16" t="s"/>
-      <x:c r="D22" s="16" t="s"/>
-      <x:c r="E22" s="17" t="s"/>
-      <x:c r="F22" s="17" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="18" t="s">
+      <x:c r="C24" s="16" t="s"/>
+      <x:c r="D24" s="16" t="s"/>
+      <x:c r="E24" s="17" t="s"/>
+      <x:c r="F24" s="17" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="18" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C23" s="19" t="s"/>
-      <x:c r="D23" s="19" t="s"/>
-      <x:c r="E23" s="19" t="s"/>
-      <x:c r="F23" s="20" t="s">
+      <x:c r="C25" s="19" t="s"/>
+      <x:c r="D25" s="19" t="s"/>
+      <x:c r="E25" s="19" t="s"/>
+      <x:c r="F25" s="20" t="s">
         <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="22" t="s"/>
-      <x:c r="F24" s="23" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C26" s="22" t="s"/>
       <x:c r="D26" s="22" t="s"/>
       <x:c r="E26" s="22" t="s"/>
       <x:c r="F26" s="23" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="24" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3134,12 +3232,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B24:F24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -17,58 +17,22 @@
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Special Radio Operator Certificate (RENEWAL)</x:t>
@@ -726,7 +690,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -753,12 +717,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -766,6 +724,43 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -787,21 +782,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -828,8 +808,19 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="17">
     <x:border/>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
@@ -855,8 +846,11 @@
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:right style="thin">
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thick">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
@@ -865,18 +859,21 @@
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
     </x:border>
     <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thick">
+      <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -890,10 +887,10 @@
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -1036,8 +1033,42 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thick">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1048,40 +1079,40 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1090,16 +1121,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1108,19 +1136,46 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -1128,49 +1183,54 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1178,7 +1238,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1190,20 +1250,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1211,31 +1271,55 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1498,769 +1582,745 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46065.33125</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45700</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216139</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46084.1560763889</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>46085.2764814815</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1216175</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>46093.2000115741</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>46065.2288541667</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1216140</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>46084.1582175926</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>46085.3007986111</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>46386</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1216177</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>46093.215162037</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46085.2858333333</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216176</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46093.2057060185</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46072.3153009259</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1216162</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>46090.311412037</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C12" s="11" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E12" s="11" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I12" s="14">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46065.33125</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45700</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216139</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46084.1560763889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46085.2764814815</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216175</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46093.2000115741</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>46065.2288541667</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216140</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>46084.1582175926</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>46085.3007986111</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>46386</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1216177</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>46093.215162037</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="D13" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F13" s="11" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G13" s="11" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H10" s="29">
-        <x:v>46085.2858333333</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>46096</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1216176</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>46093.2057060185</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="H13" s="13">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L13" s="16">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="D14" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F14" s="11" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G14" s="11" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H11" s="29">
-        <x:v>46072.3153009259</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1216162</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="H14" s="13">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="16">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46073.1095023148</x:v>
+      </x:c>
+      <x:c r="I15" s="14">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1216164</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L11" s="32">
-        <x:v>46090.311412037</x:v>
-      </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D12" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="L15" s="16">
+        <x:v>46091.121087963</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G12" s="27" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H12" s="29">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J12" s="28" t="n">
-        <x:v>1216157</x:v>
-      </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="F16" s="11" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I16" s="14">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K16" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="32">
-        <x:v>46090.267025463</x:v>
-      </x:c>
-      <x:c r="M12" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D13" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="27" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F13" s="27" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="L16" s="16">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H13" s="29">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J13" s="28" t="n">
-        <x:v>1216155</x:v>
-      </x:c>
-      <x:c r="K13" s="31" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L13" s="32">
-        <x:v>46090.2536226852</x:v>
-      </x:c>
-      <x:c r="M13" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s">
+      <x:c r="D17" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="27" t="s">
+      <x:c r="F17" s="11" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="G17" s="11" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G14" s="27" t="s">
+      <x:c r="H17" s="13">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I17" s="14">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K17" s="15" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L17" s="16">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="H14" s="29">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I14" s="30">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J14" s="28" t="n">
-        <x:v>1216153</x:v>
-      </x:c>
-      <x:c r="K14" s="31" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L14" s="32">
-        <x:v>46090.2431828704</x:v>
-      </x:c>
-      <x:c r="M14" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s">
+      <x:c r="D18" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="27" t="s">
+      <x:c r="G18" s="11" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="H18" s="13">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I18" s="14">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K18" s="15" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L18" s="16">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G15" s="27" t="s">
+      <x:c r="D19" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="H15" s="29">
-        <x:v>46073.1095023148</x:v>
-      </x:c>
-      <x:c r="I15" s="30">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J15" s="28" t="n">
-        <x:v>1216164</x:v>
-      </x:c>
-      <x:c r="K15" s="31" t="n">
+      <x:c r="F19" s="11" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I19" s="14">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K19" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L19" s="16">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I20" s="14">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K20" s="15" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L15" s="32">
-        <x:v>46091.121087963</x:v>
-      </x:c>
-      <x:c r="M15" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D16" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="27" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F16" s="27" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G16" s="27" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H16" s="29">
-        <x:v>46073.061099537</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J16" s="28" t="n">
-        <x:v>1216151</x:v>
-      </x:c>
-      <x:c r="K16" s="31" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L16" s="32">
-        <x:v>46090.2266435185</x:v>
-      </x:c>
-      <x:c r="M16" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s">
+      <x:c r="L20" s="16">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I21" s="14">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K21" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D17" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="27" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F17" s="27" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G17" s="27" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H17" s="29">
-        <x:v>46077.2683564815</x:v>
-      </x:c>
-      <x:c r="I17" s="30">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J17" s="28" t="n">
-        <x:v>1216159</x:v>
-      </x:c>
-      <x:c r="K17" s="31" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L17" s="32">
-        <x:v>46090.2806018519</x:v>
-      </x:c>
-      <x:c r="M17" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D18" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="27" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F18" s="27" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G18" s="27" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H18" s="29">
-        <x:v>46073.0763541667</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J18" s="28" t="n">
-        <x:v>1216149</x:v>
-      </x:c>
-      <x:c r="K18" s="31" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L18" s="32">
-        <x:v>46090.2162847222</x:v>
-      </x:c>
-      <x:c r="M18" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D19" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="27" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F19" s="27" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G19" s="27" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H19" s="29">
-        <x:v>46077.1834259259</x:v>
-      </x:c>
-      <x:c r="I19" s="30">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J19" s="28" t="n">
-        <x:v>1216166</x:v>
-      </x:c>
-      <x:c r="K19" s="31" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L19" s="32">
-        <x:v>46091.2388773148</x:v>
-      </x:c>
-      <x:c r="M19" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D20" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="27" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F20" s="27" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G20" s="27" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H20" s="29">
-        <x:v>46071.2853587963</x:v>
-      </x:c>
-      <x:c r="I20" s="30">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J20" s="28" t="n">
-        <x:v>1216191</x:v>
-      </x:c>
-      <x:c r="K20" s="31" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L20" s="32">
-        <x:v>46094.1777199074</x:v>
-      </x:c>
-      <x:c r="M20" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D21" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="27" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F21" s="27" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G21" s="27" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H21" s="29">
-        <x:v>46090.3681365741</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J21" s="28" t="n">
-        <x:v>1216192</x:v>
-      </x:c>
-      <x:c r="K21" s="31" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L21" s="32">
+      <x:c r="L21" s="16">
         <x:v>46094.182662037</x:v>
       </x:c>
-      <x:c r="M21" s="27" t="s">
-        <x:v>19</x:v>
+      <x:c r="M21" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C24" s="16" t="s"/>
-      <x:c r="D24" s="16" t="s"/>
-      <x:c r="E24" s="17" t="s"/>
-      <x:c r="F24" s="17" t="s"/>
+      <x:c r="B24" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C24" s="39" t="s"/>
+      <x:c r="D24" s="39" t="s"/>
+      <x:c r="E24" s="40" t="s"/>
+      <x:c r="F24" s="40" t="s"/>
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C25" s="19" t="s"/>
-      <x:c r="D25" s="19" t="s"/>
-      <x:c r="E25" s="19" t="s"/>
-      <x:c r="F25" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B25" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="23" t="n">
+      <x:c r="B26" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s"/>
-      <x:c r="D27" s="22" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="23" t="n">
+      <x:c r="B27" s="24" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="23" t="n">
+      <x:c r="B28" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
+      <x:c r="B29" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -3313,190 +3373,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>45861.181087963</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215835</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45862.1344560185</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s"/>
+      <x:c r="C7" s="17" t="s"/>
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s"/>
+      <x:c r="F7" s="17" t="s"/>
+      <x:c r="G7" s="17" t="s"/>
+      <x:c r="H7" s="17" t="s"/>
+      <x:c r="I7" s="17" t="s"/>
+      <x:c r="J7" s="17" t="s"/>
+      <x:c r="K7" s="17" t="s"/>
+      <x:c r="L7" s="17" t="s"/>
+      <x:c r="M7" s="17" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="18" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="C9" s="19" t="s"/>
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B10" s="21" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="C10" s="22" t="s"/>
+      <x:c r="D10" s="22" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="23" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B11" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="25" t="s"/>
+      <x:c r="F11" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B12" s="27" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45861.181087963</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215835</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45862.1344560185</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4564,487 +4620,463 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45881.1074421296</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45889</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1195698</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45882.1141782407</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>45881.2688541667</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1346458</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>45882.0237847222</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45875.2668402778</x:v>
+      </x:c>
+      <x:c r="I9" s="35">
+        <x:v>45875.2668518519</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1215854</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>45877.2327314815</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>45889.2616782407</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>45889.2616898148</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215867</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45891.1582986111</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>45889.1521064815</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>44272</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1215866</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>45891.153287037</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>45887.5499305556</x:v>
+      </x:c>
+      <x:c r="I12" s="13">
+        <x:v>45887.5499537037</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>45891.1027199074</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C13" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45881.1074421296</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45889</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1195698</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45882.1141782407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45875.2668402778</x:v>
-      </x:c>
-      <x:c r="I9" s="29">
-        <x:v>45875.2668518519</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1215854</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>45877.2327314815</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="E13" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="F13" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H10" s="29">
-        <x:v>45889.2616782407</x:v>
-      </x:c>
-      <x:c r="I10" s="29">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1215867</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>45891.1582986111</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="G13" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
-        <x:v>45889.1521064815</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>44272</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1215866</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="L11" s="32">
-        <x:v>45891.153287037</x:v>
-      </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D12" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E12" s="27" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F12" s="27" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G12" s="27" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H12" s="29">
-        <x:v>45887.5499305556</x:v>
-      </x:c>
-      <x:c r="I12" s="29">
-        <x:v>45887.5499537037</x:v>
-      </x:c>
-      <x:c r="J12" s="28" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K12" s="31" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="32">
-        <x:v>45891.1027199074</x:v>
-      </x:c>
-      <x:c r="M12" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D13" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F13" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G13" s="27" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="13">
         <x:v>45883.2595717593</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="14">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="12" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="15" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="16">
         <x:v>45883.2880208333</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
-        <x:v>34</x:v>
+      <x:c r="M13" s="11" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s"/>
-      <x:c r="D16" s="16" t="s"/>
-      <x:c r="E16" s="17" t="s"/>
-      <x:c r="F16" s="17" t="s"/>
+      <x:c r="B16" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C16" s="39" t="s"/>
+      <x:c r="D16" s="39" t="s"/>
+      <x:c r="E16" s="40" t="s"/>
+      <x:c r="F16" s="40" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="19" t="s"/>
-      <x:c r="F17" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B17" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
+      <x:c r="B21" s="24" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="n">
+      <x:c r="B22" s="24" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="B23" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6105,389 +6137,365 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45902.1777546296</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45781</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215887</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45911.9486574074</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>45887.2917592593</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1215880</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>45903.1177546296</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1215899</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45918.0952083333</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C9" s="34" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E9" s="34" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45925.3972453704</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>47021</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1215915</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>45930.1169560185</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45902.1777546296</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45781</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215887</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45911.9486574074</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
+      <x:c r="H10" s="13">
+        <x:v>45916.1769097222</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215916</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45930.1671643518</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F8" s="27" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G8" s="27" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="I8" s="29">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1215899</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45918.0952083333</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45925.3972453704</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>47021</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1215915</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>45930.1169560185</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>45916.1769097222</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1215916</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>45930.1671643518</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="13">
         <x:v>45912.47375</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="14">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:v>1215898</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="16">
         <x:v>45918.0905787037</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s"/>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="17" t="s"/>
-      <x:c r="F14" s="17" t="s"/>
+      <x:c r="B14" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="39" t="s"/>
+      <x:c r="D14" s="39" t="s"/>
+      <x:c r="E14" s="40" t="s"/>
+      <x:c r="F14" s="40" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B15" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
+      <x:c r="B19" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7550,226 +7558,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45938.0053703704</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215952</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45945.1196180556</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C7" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E7" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>45945.2727662037</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45911</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1215958</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>45953.151099537</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="38" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="C10" s="39" t="s"/>
+      <x:c r="D10" s="39" t="s"/>
+      <x:c r="E10" s="40" t="s"/>
+      <x:c r="F10" s="40" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="21" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="23" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45938.0053703704</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215952</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45945.1196180556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45945.2727662037</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45911</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215958</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45953.151099537</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8836,340 +8846,316 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45944.1129282407</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215998</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45971.316400463</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>45954.1265625</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45626</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1215975</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>45967.0018287037</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45965.2541435185</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45971</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1215995</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45971.1502199074</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C9" s="34" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E9" s="34" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45966.1203125</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1216011</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>45975.3046180556</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45954.1265625</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45626</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215975</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45967.0018287037</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45965.2541435185</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45971</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1215995</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
+      <x:c r="H10" s="13">
+        <x:v>45966.1218055556</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216012</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45971.1502199074</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45966.1203125</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1216011</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>45975.3046180556</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>45966.1218055556</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1216012</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="16">
         <x:v>45975.312349537</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s"/>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="17" t="s"/>
-      <x:c r="F13" s="17" t="s"/>
+      <x:c r="B13" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="39" t="s"/>
+      <x:c r="D13" s="39" t="s"/>
+      <x:c r="E13" s="40" t="s"/>
+      <x:c r="F13" s="40" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B14" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -10233,215 +10219,217 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45979.0549768519</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46006.2690046296</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>45972.2314236111</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1216026</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>45992.0065509259</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" s="39" t="s"/>
+      <x:c r="D10" s="39" t="s"/>
+      <x:c r="E10" s="40" t="s"/>
+      <x:c r="F10" s="40" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="23" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B13" s="27" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45979.0549768519</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46006.2690046296</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45972.2314236111</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216026</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45992.0065509259</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -11508,398 +11496,374 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46007.2920138889</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46007.292037037</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1195956</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46044.2434953704</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>46031.042974537</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1216079</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>46043.2977199074</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>46029.1168055556</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1216071</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>46036.0526736111</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C9" s="34" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E9" s="34" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>46029.112962963</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1216072</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>46036.0583564815</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46036.929224537</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216095</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46050.0472337963</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46007.2920138889</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46007.292037037</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1195956</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46044.2434953704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F8" s="27" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>46036.0526736111</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>46029.112962963</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1216072</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
+      <x:c r="H11" s="13">
+        <x:v>46034.1741087963</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1216082</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="32">
-        <x:v>46036.0583564815</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>46036.929224537</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1216095</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>46050.0472337963</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="16">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s"/>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="17" t="s"/>
-      <x:c r="F14" s="17" t="s"/>
+      <x:c r="B14" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="39" t="s"/>
+      <x:c r="D14" s="39" t="s"/>
+      <x:c r="E14" s="40" t="s"/>
+      <x:c r="F14" s="40" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B15" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="B20" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -12962,351 +12926,327 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46072.0406597222</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46077.0821759259</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1195996</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46078.028275463</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>46050.1475925926</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1216105</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>46057.9737731482</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>46057.234375</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1216128</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>46072.0668055556</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>46066.1502662037</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1216135</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>46077.9542708333</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C10" s="11" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E10" s="11" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46051.2882638889</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>44445</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216104</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46057.963587963</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46072.0406597222</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46077.0821759259</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1195996</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46078.028275463</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>46057.234375</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216128</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>46072.0668055556</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>46066.1502662037</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1216135</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>46077.9542708333</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>46051.2882638889</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>44445</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1216104</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>46057.963587963</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s"/>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="17" t="s"/>
-      <x:c r="F13" s="17" t="s"/>
+      <x:c r="B13" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="39" t="s"/>
+      <x:c r="D13" s="39" t="s"/>
+      <x:c r="E13" s="40" t="s"/>
+      <x:c r="F13" s="40" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B14" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="24" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1567,7 +1567,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1637,7 +1637,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>12</x:v>
@@ -3385,7 +3385,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3455,7 +3455,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s"/>
       <x:c r="C7" s="17" t="s"/>
@@ -4639,7 +4639,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -4709,7 +4709,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>12</x:v>
@@ -6183,7 +6183,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -6253,7 +6253,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>12</x:v>
@@ -7631,7 +7631,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -7701,7 +7701,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>1</x:v>
@@ -8920,7 +8920,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -8990,7 +8990,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>12</x:v>
@@ -10320,7 +10320,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -10390,7 +10390,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>1</x:v>
@@ -11598,7 +11598,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -11666,7 +11666,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>12</x:v>
@@ -13055,7 +13055,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -13125,7 +13125,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>12</x:v>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,9 +30,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <x:si>
     <x:t>CERTIFICATE SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Special Radio Operator Certificate (RENEWAL)</x:t>
@@ -690,7 +726,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -735,15 +771,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -763,18 +799,10 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -1009,7 +1037,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1020,10 +1048,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1033,15 +1067,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1065,10 +1090,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1080,26 +1108,14 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1130,40 +1146,24 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1190,15 +1190,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1214,63 +1214,27 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1569,18 +1533,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1598,709 +1550,721 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46065.33125</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45700</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216139</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46084.1560763889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>46085.2764814815</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1216175</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>46093.2000115741</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G8" s="35" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H8" s="36">
+      <x:c r="B8" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46065.33125</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45700</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216139</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46084.1560763889</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46085.2764814815</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216175</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46093.2000115741</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>46065.2288541667</x:v>
       </x:c>
-      <x:c r="I8" s="37">
+      <x:c r="I10" s="30">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J8" s="35" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1216140</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="36">
+      <x:c r="L10" s="32">
         <x:v>46084.1582175926</x:v>
       </x:c>
-      <x:c r="M8" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G9" s="35" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H9" s="36">
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>46085.3007986111</x:v>
       </x:c>
-      <x:c r="I9" s="37">
+      <x:c r="I11" s="30">
         <x:v>46386</x:v>
       </x:c>
-      <x:c r="J9" s="35" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216177</x:v>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="36">
+      <x:c r="L11" s="32">
         <x:v>46093.215162037</x:v>
       </x:c>
-      <x:c r="M9" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>46085.2858333333</x:v>
       </x:c>
-      <x:c r="I10" s="44">
+      <x:c r="I12" s="30">
         <x:v>46096</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1216176</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>46093.2057060185</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
         <x:v>46072.3153009259</x:v>
       </x:c>
-      <x:c r="I11" s="44">
+      <x:c r="I13" s="30">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="28" t="n">
         <x:v>1216162</x:v>
       </x:c>
-      <x:c r="K11" s="42" t="n">
+      <x:c r="K13" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="32">
         <x:v>46090.311412037</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
         <x:v>46073.0262847222</x:v>
       </x:c>
-      <x:c r="I12" s="44">
+      <x:c r="I14" s="30">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J14" s="28" t="n">
         <x:v>1216157</x:v>
       </x:c>
-      <x:c r="K12" s="42" t="n">
+      <x:c r="K14" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="43">
+      <x:c r="L14" s="32">
         <x:v>46090.267025463</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F13" s="39" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G13" s="39" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H13" s="41">
+      <x:c r="M14" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F15" s="27" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H15" s="29">
         <x:v>46077.2103587963</x:v>
       </x:c>
-      <x:c r="I13" s="44">
+      <x:c r="I15" s="30">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J15" s="28" t="n">
         <x:v>1216155</x:v>
       </x:c>
-      <x:c r="K13" s="42" t="n">
+      <x:c r="K15" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="43">
+      <x:c r="L15" s="32">
         <x:v>46090.2536226852</x:v>
       </x:c>
-      <x:c r="M13" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="39" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D14" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="39" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F14" s="39" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G14" s="39" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H14" s="41">
+      <x:c r="M15" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H16" s="29">
         <x:v>46073.0478472222</x:v>
       </x:c>
-      <x:c r="I14" s="44">
+      <x:c r="I16" s="30">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J14" s="40" t="n">
+      <x:c r="J16" s="28" t="n">
         <x:v>1216153</x:v>
       </x:c>
-      <x:c r="K14" s="42" t="n">
+      <x:c r="K16" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L14" s="43">
+      <x:c r="L16" s="32">
         <x:v>46090.2431828704</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D15" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F15" s="39" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G15" s="39" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H15" s="41">
+      <x:c r="M16" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F17" s="27" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H17" s="29">
         <x:v>46073.1095023148</x:v>
       </x:c>
-      <x:c r="I15" s="44">
+      <x:c r="I17" s="30">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J17" s="28" t="n">
         <x:v>1216164</x:v>
       </x:c>
-      <x:c r="K15" s="42" t="n">
+      <x:c r="K17" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L15" s="43">
+      <x:c r="L17" s="32">
         <x:v>46091.121087963</x:v>
       </x:c>
-      <x:c r="M15" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D16" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F16" s="39" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G16" s="39" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H16" s="41">
+      <x:c r="M17" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F18" s="27" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H18" s="29">
         <x:v>46073.061099537</x:v>
       </x:c>
-      <x:c r="I16" s="44">
+      <x:c r="I18" s="30">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J16" s="40" t="n">
+      <x:c r="J18" s="28" t="n">
         <x:v>1216151</x:v>
       </x:c>
-      <x:c r="K16" s="42" t="n">
+      <x:c r="K18" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="43">
+      <x:c r="L18" s="32">
         <x:v>46090.2266435185</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="39" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D17" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E17" s="39" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F17" s="39" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G17" s="39" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H17" s="41">
+      <x:c r="M18" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D19" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="27" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F19" s="27" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G19" s="27" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H19" s="29">
         <x:v>46077.2683564815</x:v>
       </x:c>
-      <x:c r="I17" s="44">
+      <x:c r="I19" s="30">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J19" s="28" t="n">
         <x:v>1216159</x:v>
       </x:c>
-      <x:c r="K17" s="42" t="n">
+      <x:c r="K19" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L17" s="43">
+      <x:c r="L19" s="32">
         <x:v>46090.2806018519</x:v>
       </x:c>
-      <x:c r="M17" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="39" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D18" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E18" s="39" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F18" s="39" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G18" s="39" t="s">
+      <x:c r="M19" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D20" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="27" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="H18" s="41">
+      <x:c r="F20" s="27" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G20" s="27" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H20" s="29">
         <x:v>46073.0763541667</x:v>
       </x:c>
-      <x:c r="I18" s="44">
+      <x:c r="I20" s="30">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J18" s="40" t="n">
+      <x:c r="J20" s="28" t="n">
         <x:v>1216149</x:v>
       </x:c>
-      <x:c r="K18" s="42" t="n">
+      <x:c r="K20" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L18" s="43">
+      <x:c r="L20" s="32">
         <x:v>46090.2162847222</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="39" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D19" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" s="39" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F19" s="39" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G19" s="39" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H19" s="41">
+      <x:c r="M20" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D21" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="27" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F21" s="27" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G21" s="27" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H21" s="29">
         <x:v>46077.1834259259</x:v>
       </x:c>
-      <x:c r="I19" s="44">
+      <x:c r="I21" s="30">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J21" s="28" t="n">
         <x:v>1216166</x:v>
       </x:c>
-      <x:c r="K19" s="42" t="n">
+      <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L19" s="43">
+      <x:c r="L21" s="32">
         <x:v>46091.2388773148</x:v>
       </x:c>
-      <x:c r="M19" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="39" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D20" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E20" s="39" t="s">
+      <x:c r="M21" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="27" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F22" s="27" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G22" s="27" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H22" s="29">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I22" s="30">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J22" s="28" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K22" s="31" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L22" s="32">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M22" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D23" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E23" s="27" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F23" s="27" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G23" s="27" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H23" s="29">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J23" s="28" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G20" s="39" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H20" s="41">
-        <x:v>46071.2853587963</x:v>
-      </x:c>
-      <x:c r="I20" s="44">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J20" s="40" t="n">
-        <x:v>1216191</x:v>
-      </x:c>
-      <x:c r="K20" s="42" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L20" s="43">
-        <x:v>46094.1777199074</x:v>
-      </x:c>
-      <x:c r="M20" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="39" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D21" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E21" s="39" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F21" s="39" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G21" s="39" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H21" s="41">
-        <x:v>46090.3681365741</x:v>
-      </x:c>
-      <x:c r="I21" s="44">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J21" s="40" t="n">
-        <x:v>1216192</x:v>
-      </x:c>
-      <x:c r="K21" s="42" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L21" s="43">
+      <x:c r="L23" s="32">
         <x:v>46094.182662037</x:v>
       </x:c>
-      <x:c r="M21" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B22" s="45" t="s"/>
-      <x:c r="C22" s="45" t="s"/>
-      <x:c r="D22" s="45" t="s"/>
-      <x:c r="E22" s="45" t="s"/>
-      <x:c r="F22" s="45" t="s"/>
-      <x:c r="G22" s="45" t="s"/>
-      <x:c r="H22" s="45" t="s"/>
-      <x:c r="I22" s="45" t="s"/>
-      <x:c r="J22" s="45" t="s"/>
-      <x:c r="K22" s="45" t="s"/>
-      <x:c r="L22" s="45" t="s"/>
-      <x:c r="M22" s="45" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B23" s="45" t="s"/>
-      <x:c r="C23" s="45" t="s"/>
-      <x:c r="D23" s="45" t="s"/>
-      <x:c r="E23" s="45" t="s"/>
-      <x:c r="F23" s="45" t="s"/>
-      <x:c r="G23" s="45" t="s"/>
-      <x:c r="H23" s="45" t="s"/>
-      <x:c r="I23" s="45" t="s"/>
-      <x:c r="J23" s="45" t="s"/>
-      <x:c r="K23" s="45" t="s"/>
-      <x:c r="L23" s="45" t="s"/>
-      <x:c r="M23" s="45" t="s"/>
+      <x:c r="M23" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C26" s="20" t="s"/>
-      <x:c r="D26" s="20" t="s"/>
-      <x:c r="E26" s="21" t="s"/>
-      <x:c r="F26" s="21" t="s"/>
+      <x:c r="B26" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="s"/>
+      <x:c r="D26" s="16" t="s"/>
+      <x:c r="E26" s="17" t="s"/>
+      <x:c r="F26" s="17" t="s"/>
     </x:row>
     <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="24" t="s">
+      <x:c r="B27" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C27" s="19" t="s"/>
+      <x:c r="D27" s="19" t="s"/>
+      <x:c r="E27" s="19" t="s"/>
+      <x:c r="F27" s="20" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C29" s="22" t="s"/>
+      <x:c r="D29" s="22" t="s"/>
+      <x:c r="E29" s="22" t="s"/>
+      <x:c r="F29" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C30" s="22" t="s"/>
+      <x:c r="D30" s="22" t="s"/>
+      <x:c r="E30" s="22" t="s"/>
+      <x:c r="F30" s="23" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
     <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
+      <x:c r="B31" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -3387,18 +3351,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3416,75 +3368,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45861.181087963</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215835</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45862.1344560185</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s"/>
-      <x:c r="C7" s="17" t="s"/>
-      <x:c r="D7" s="17" t="s"/>
-      <x:c r="E7" s="17" t="s"/>
-      <x:c r="F7" s="17" t="s"/>
-      <x:c r="G7" s="17" t="s"/>
-      <x:c r="H7" s="17" t="s"/>
-      <x:c r="I7" s="17" t="s"/>
-      <x:c r="J7" s="17" t="s"/>
-      <x:c r="K7" s="17" t="s"/>
-      <x:c r="L7" s="17" t="s"/>
-      <x:c r="M7" s="17" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="18" t="s"/>
-      <x:c r="C8" s="18" t="s"/>
-      <x:c r="D8" s="18" t="s"/>
-      <x:c r="E8" s="18" t="s"/>
-      <x:c r="F8" s="18" t="s"/>
-      <x:c r="G8" s="18" t="s"/>
-      <x:c r="H8" s="18" t="s"/>
-      <x:c r="I8" s="18" t="s"/>
-      <x:c r="J8" s="18" t="s"/>
-      <x:c r="K8" s="18" t="s"/>
-      <x:c r="L8" s="18" t="s"/>
-      <x:c r="M8" s="18" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45861.181087963</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215835</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45862.1344560185</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3502,44 +3466,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
+      <x:c r="B11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B12" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
+      <x:c r="B13" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4641,18 +4605,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4670,427 +4622,439 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45881.1074421296</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45889</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1195698</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45882.1141782407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F8" s="35" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G8" s="35" t="s">
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H8" s="36">
+      <x:c r="F8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45881.1074421296</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45889</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1195698</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45882.1141782407</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45881.2688541667</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346458</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45882.0237847222</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45897.2409837963</x:v>
       </x:c>
-      <x:c r="I8" s="37">
+      <x:c r="I10" s="30">
         <x:v>45681</x:v>
       </x:c>
-      <x:c r="J8" s="35" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1346493</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="36">
+      <x:c r="L10" s="32">
         <x:v>45897.2777430556</x:v>
       </x:c>
-      <x:c r="M8" s="35" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="35" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G9" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H9" s="36">
+      <x:c r="M10" s="27" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>45875.2668402778</x:v>
       </x:c>
-      <x:c r="I9" s="36">
+      <x:c r="I11" s="29">
         <x:v>45875.2668518519</x:v>
       </x:c>
-      <x:c r="J9" s="35" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1215854</x:v>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="36">
+      <x:c r="L11" s="32">
         <x:v>45877.2327314815</x:v>
       </x:c>
-      <x:c r="M9" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
+      <x:c r="M11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
+        <x:v>45889.2616782407</x:v>
+      </x:c>
+      <x:c r="I12" s="29">
+        <x:v>45889.2616898148</x:v>
+      </x:c>
+      <x:c r="J12" s="28" t="n">
+        <x:v>1215867</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L12" s="32">
+        <x:v>45891.1582986111</x:v>
+      </x:c>
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
+        <x:v>45889.1521064815</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>44272</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
+        <x:v>1215866</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L13" s="32">
+        <x:v>45891.153287037</x:v>
+      </x:c>
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
+        <x:v>45887.5499305556</x:v>
+      </x:c>
+      <x:c r="I14" s="29">
+        <x:v>45887.5499537037</x:v>
+      </x:c>
+      <x:c r="J14" s="28" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L14" s="32">
+        <x:v>45891.1027199074</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F15" s="27" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H15" s="29">
+        <x:v>45883.2595717593</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="L15" s="32">
+        <x:v>45883.2880208333</x:v>
+      </x:c>
+      <x:c r="M15" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
-        <x:v>45889.2616782407</x:v>
-      </x:c>
-      <x:c r="I10" s="41">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J10" s="40" t="n">
-        <x:v>1215867</x:v>
-      </x:c>
-      <x:c r="K10" s="42" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L10" s="43">
-        <x:v>45891.1582986111</x:v>
-      </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
-        <x:v>45889.1521064815</x:v>
-      </x:c>
-      <x:c r="I11" s="44">
-        <x:v>44272</x:v>
-      </x:c>
-      <x:c r="J11" s="40" t="n">
-        <x:v>1215866</x:v>
-      </x:c>
-      <x:c r="K11" s="42" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="L11" s="43">
-        <x:v>45891.153287037</x:v>
-      </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="39" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
-        <x:v>45887.5499305556</x:v>
-      </x:c>
-      <x:c r="I12" s="41">
-        <x:v>45887.5499537037</x:v>
-      </x:c>
-      <x:c r="J12" s="40" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K12" s="42" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="43">
-        <x:v>45891.1027199074</x:v>
-      </x:c>
-      <x:c r="M12" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F13" s="39" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G13" s="39" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H13" s="41">
-        <x:v>45883.2595717593</x:v>
-      </x:c>
-      <x:c r="I13" s="44">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J13" s="40" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K13" s="42" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="L13" s="43">
-        <x:v>45883.2880208333</x:v>
-      </x:c>
-      <x:c r="M13" s="39" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="45" t="s"/>
-      <x:c r="C14" s="45" t="s"/>
-      <x:c r="D14" s="45" t="s"/>
-      <x:c r="E14" s="45" t="s"/>
-      <x:c r="F14" s="45" t="s"/>
-      <x:c r="G14" s="45" t="s"/>
-      <x:c r="H14" s="45" t="s"/>
-      <x:c r="I14" s="45" t="s"/>
-      <x:c r="J14" s="45" t="s"/>
-      <x:c r="K14" s="45" t="s"/>
-      <x:c r="L14" s="45" t="s"/>
-      <x:c r="M14" s="45" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B15" s="45" t="s"/>
-      <x:c r="C15" s="45" t="s"/>
-      <x:c r="D15" s="45" t="s"/>
-      <x:c r="E15" s="45" t="s"/>
-      <x:c r="F15" s="45" t="s"/>
-      <x:c r="G15" s="45" t="s"/>
-      <x:c r="H15" s="45" t="s"/>
-      <x:c r="I15" s="45" t="s"/>
-      <x:c r="J15" s="45" t="s"/>
-      <x:c r="K15" s="45" t="s"/>
-      <x:c r="L15" s="45" t="s"/>
-      <x:c r="M15" s="45" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="s"/>
-      <x:c r="D18" s="20" t="s"/>
-      <x:c r="E18" s="21" t="s"/>
-      <x:c r="F18" s="21" t="s"/>
+      <x:c r="B18" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s"/>
+      <x:c r="D18" s="16" t="s"/>
+      <x:c r="E18" s="17" t="s"/>
+      <x:c r="F18" s="17" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B19" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C19" s="19" t="s"/>
+      <x:c r="D19" s="19" t="s"/>
+      <x:c r="E19" s="19" t="s"/>
+      <x:c r="F19" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
+      <x:c r="B20" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
+      <x:c r="B21" s="21" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
+      <x:c r="B22" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="22" t="s"/>
+      <x:c r="F22" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
+      <x:c r="B23" s="21" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="s"/>
+      <x:c r="D23" s="22" t="s"/>
+      <x:c r="E23" s="22" t="s"/>
+      <x:c r="F23" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
+      <x:c r="B24" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="22" t="s"/>
+      <x:c r="F24" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="30" t="n">
+      <x:c r="B25" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6185,18 +6149,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6214,329 +6166,341 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45902.1777546296</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45781</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215887</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45911.9486574074</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="35" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45902.1777546296</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45781</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215887</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45911.9486574074</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45887.2917592593</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215880</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45903.1177546296</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G8" s="35" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H8" s="36">
+      <x:c r="E10" s="27" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45911.4396296296</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="29">
         <x:v>45911.4396296296</x:v>
       </x:c>
-      <x:c r="J8" s="35" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1215899</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="36">
+      <x:c r="L10" s="32">
         <x:v>45918.0952083333</x:v>
       </x:c>
-      <x:c r="M8" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G9" s="35" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H9" s="36">
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>45925.3972453704</x:v>
       </x:c>
-      <x:c r="I9" s="37">
+      <x:c r="I11" s="30">
         <x:v>47021</x:v>
       </x:c>
-      <x:c r="J9" s="35" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1215915</x:v>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L9" s="36">
+      <x:c r="L11" s="32">
         <x:v>45930.1169560185</x:v>
       </x:c>
-      <x:c r="M9" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>45916.1769097222</x:v>
       </x:c>
-      <x:c r="I10" s="44">
+      <x:c r="I12" s="30">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1215916</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>45930.1671643518</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
         <x:v>45912.47375</x:v>
       </x:c>
-      <x:c r="I11" s="44">
+      <x:c r="I13" s="30">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="28" t="n">
         <x:v>1215898</x:v>
       </x:c>
-      <x:c r="K11" s="42" t="n">
+      <x:c r="K13" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="32">
         <x:v>45918.0905787037</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="45" t="s"/>
-      <x:c r="C12" s="45" t="s"/>
-      <x:c r="D12" s="45" t="s"/>
-      <x:c r="E12" s="45" t="s"/>
-      <x:c r="F12" s="45" t="s"/>
-      <x:c r="G12" s="45" t="s"/>
-      <x:c r="H12" s="45" t="s"/>
-      <x:c r="I12" s="45" t="s"/>
-      <x:c r="J12" s="45" t="s"/>
-      <x:c r="K12" s="45" t="s"/>
-      <x:c r="L12" s="45" t="s"/>
-      <x:c r="M12" s="45" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="45" t="s"/>
-      <x:c r="C13" s="45" t="s"/>
-      <x:c r="D13" s="45" t="s"/>
-      <x:c r="E13" s="45" t="s"/>
-      <x:c r="F13" s="45" t="s"/>
-      <x:c r="G13" s="45" t="s"/>
-      <x:c r="H13" s="45" t="s"/>
-      <x:c r="I13" s="45" t="s"/>
-      <x:c r="J13" s="45" t="s"/>
-      <x:c r="K13" s="45" t="s"/>
-      <x:c r="L13" s="45" t="s"/>
-      <x:c r="M13" s="45" t="s"/>
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
+      <x:c r="B16" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s"/>
+      <x:c r="D16" s="16" t="s"/>
+      <x:c r="E16" s="17" t="s"/>
+      <x:c r="F16" s="17" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B17" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="19" t="s"/>
+      <x:c r="F17" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="B19" s="21" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
+      <x:c r="B20" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="B21" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7633,18 +7597,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7662,166 +7614,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45938.0053703704</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215952</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45945.1196180556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45938.0053703704</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215952</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45945.1196180556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
         <x:v>45945.2727662037</x:v>
       </x:c>
-      <x:c r="I7" s="33">
+      <x:c r="I9" s="13">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J7" s="31" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>1215958</x:v>
       </x:c>
-      <x:c r="K7" s="34" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L7" s="32">
+      <x:c r="L9" s="12">
         <x:v>45953.151099537</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="18" t="s"/>
-      <x:c r="C8" s="18" t="s"/>
-      <x:c r="D8" s="18" t="s"/>
-      <x:c r="E8" s="18" t="s"/>
-      <x:c r="F8" s="18" t="s"/>
-      <x:c r="G8" s="18" t="s"/>
-      <x:c r="H8" s="18" t="s"/>
-      <x:c r="I8" s="18" t="s"/>
-      <x:c r="J8" s="18" t="s"/>
-      <x:c r="K8" s="18" t="s"/>
-      <x:c r="L8" s="18" t="s"/>
-      <x:c r="M8" s="18" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="18" t="s"/>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="18" t="s"/>
-      <x:c r="F9" s="18" t="s"/>
-      <x:c r="G9" s="18" t="s"/>
-      <x:c r="H9" s="18" t="s"/>
-      <x:c r="I9" s="18" t="s"/>
-      <x:c r="J9" s="18" t="s"/>
-      <x:c r="K9" s="18" t="s"/>
-      <x:c r="L9" s="18" t="s"/>
-      <x:c r="M9" s="18" t="s"/>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
+      <x:c r="B15" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8922,18 +8886,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8951,280 +8903,292 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>45954.1265625</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45626</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1215975</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>45967.0018287037</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G8" s="35" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H8" s="36">
+      <x:c r="B8" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45944.1129282407</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215998</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45971.316400463</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45954.1265625</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45626</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215975</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45967.0018287037</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45965.2541435185</x:v>
       </x:c>
-      <x:c r="I8" s="37">
+      <x:c r="I10" s="30">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="J8" s="35" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1215995</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="36">
+      <x:c r="L10" s="32">
         <x:v>45971.1502199074</x:v>
       </x:c>
-      <x:c r="M8" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G9" s="35" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H9" s="36">
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>45966.1203125</x:v>
       </x:c>
-      <x:c r="I9" s="37">
+      <x:c r="I11" s="30">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J9" s="35" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216011</x:v>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="36">
+      <x:c r="L11" s="32">
         <x:v>45975.3046180556</x:v>
       </x:c>
-      <x:c r="M9" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>45966.1218055556</x:v>
       </x:c>
-      <x:c r="I10" s="44">
+      <x:c r="I12" s="30">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1216012</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>45975.312349537</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="45" t="s"/>
-      <x:c r="C11" s="45" t="s"/>
-      <x:c r="D11" s="45" t="s"/>
-      <x:c r="E11" s="45" t="s"/>
-      <x:c r="F11" s="45" t="s"/>
-      <x:c r="G11" s="45" t="s"/>
-      <x:c r="H11" s="45" t="s"/>
-      <x:c r="I11" s="45" t="s"/>
-      <x:c r="J11" s="45" t="s"/>
-      <x:c r="K11" s="45" t="s"/>
-      <x:c r="L11" s="45" t="s"/>
-      <x:c r="M11" s="45" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="45" t="s"/>
-      <x:c r="C12" s="45" t="s"/>
-      <x:c r="D12" s="45" t="s"/>
-      <x:c r="E12" s="45" t="s"/>
-      <x:c r="F12" s="45" t="s"/>
-      <x:c r="G12" s="45" t="s"/>
-      <x:c r="H12" s="45" t="s"/>
-      <x:c r="I12" s="45" t="s"/>
-      <x:c r="J12" s="45" t="s"/>
-      <x:c r="K12" s="45" t="s"/>
-      <x:c r="L12" s="45" t="s"/>
-      <x:c r="M12" s="45" t="s"/>
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
+      <x:c r="B15" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s"/>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="17" t="s"/>
+      <x:c r="F15" s="17" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B16" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -10322,18 +10286,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10351,155 +10303,167 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45979.0549768519</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46006.2690046296</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45979.0549768519</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46006.2690046296</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
         <x:v>45972.2314236111</x:v>
       </x:c>
-      <x:c r="I7" s="33">
+      <x:c r="I9" s="13">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J7" s="31" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>1216026</x:v>
       </x:c>
-      <x:c r="K7" s="34" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L7" s="32">
+      <x:c r="L9" s="12">
         <x:v>45992.0065509259</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="18" t="s"/>
-      <x:c r="C8" s="18" t="s"/>
-      <x:c r="D8" s="18" t="s"/>
-      <x:c r="E8" s="18" t="s"/>
-      <x:c r="F8" s="18" t="s"/>
-      <x:c r="G8" s="18" t="s"/>
-      <x:c r="H8" s="18" t="s"/>
-      <x:c r="I8" s="18" t="s"/>
-      <x:c r="J8" s="18" t="s"/>
-      <x:c r="K8" s="18" t="s"/>
-      <x:c r="L8" s="18" t="s"/>
-      <x:c r="M8" s="18" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="18" t="s"/>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="18" t="s"/>
-      <x:c r="F9" s="18" t="s"/>
-      <x:c r="G9" s="18" t="s"/>
-      <x:c r="H9" s="18" t="s"/>
-      <x:c r="I9" s="18" t="s"/>
-      <x:c r="J9" s="18" t="s"/>
-      <x:c r="K9" s="18" t="s"/>
-      <x:c r="L9" s="18" t="s"/>
-      <x:c r="M9" s="18" t="s"/>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -11600,18 +11564,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11629,338 +11581,350 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46007.2920138889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46007.292037037</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1195956</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46044.2434953704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="35" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G8" s="35" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H8" s="36">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46007.2920138889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46007.292037037</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1195956</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46044.2434953704</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46031.042974537</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216079</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46043.2977199074</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>46029.1168055556</x:v>
       </x:c>
-      <x:c r="I8" s="37">
+      <x:c r="I10" s="30">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J8" s="35" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1216071</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="36">
+      <x:c r="L10" s="32">
         <x:v>46036.0526736111</x:v>
       </x:c>
-      <x:c r="M8" s="35" t="s">
-        <x:v>123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G9" s="35" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H9" s="36">
+      <x:c r="M10" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>46029.112962963</x:v>
       </x:c>
-      <x:c r="I9" s="37">
+      <x:c r="I11" s="30">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J9" s="35" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216072</x:v>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="36">
+      <x:c r="L11" s="32">
         <x:v>46036.0583564815</x:v>
       </x:c>
-      <x:c r="M9" s="35" t="s">
-        <x:v>123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>46036.929224537</x:v>
       </x:c>
-      <x:c r="I10" s="44">
+      <x:c r="I12" s="30">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1216095</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>46050.0472337963</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
         <x:v>46034.1741087963</x:v>
       </x:c>
-      <x:c r="I11" s="44">
+      <x:c r="I13" s="30">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="28" t="n">
         <x:v>1216082</x:v>
       </x:c>
-      <x:c r="K11" s="42" t="n">
+      <x:c r="K13" s="31" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="32">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="45" t="s"/>
-      <x:c r="C12" s="45" t="s"/>
-      <x:c r="D12" s="45" t="s"/>
-      <x:c r="E12" s="45" t="s"/>
-      <x:c r="F12" s="45" t="s"/>
-      <x:c r="G12" s="45" t="s"/>
-      <x:c r="H12" s="45" t="s"/>
-      <x:c r="I12" s="45" t="s"/>
-      <x:c r="J12" s="45" t="s"/>
-      <x:c r="K12" s="45" t="s"/>
-      <x:c r="L12" s="45" t="s"/>
-      <x:c r="M12" s="45" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="45" t="s"/>
-      <x:c r="C13" s="45" t="s"/>
-      <x:c r="D13" s="45" t="s"/>
-      <x:c r="E13" s="45" t="s"/>
-      <x:c r="F13" s="45" t="s"/>
-      <x:c r="G13" s="45" t="s"/>
-      <x:c r="H13" s="45" t="s"/>
-      <x:c r="I13" s="45" t="s"/>
-      <x:c r="J13" s="45" t="s"/>
-      <x:c r="K13" s="45" t="s"/>
-      <x:c r="L13" s="45" t="s"/>
-      <x:c r="M13" s="45" t="s"/>
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
+      <x:c r="B16" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s"/>
+      <x:c r="D16" s="16" t="s"/>
+      <x:c r="E16" s="17" t="s"/>
+      <x:c r="F16" s="17" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B17" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="19" t="s"/>
+      <x:c r="F17" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="B19" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
+      <x:c r="B20" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
+      <x:c r="B21" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
+      <x:c r="B22" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -13057,18 +13021,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13086,291 +13038,303 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46072.0406597222</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46077.0821759259</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1195996</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46078.028275463</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G8" s="35" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H8" s="36">
+      <x:c r="C8" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46072.0406597222</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46077.0821759259</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1195996</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46078.028275463</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46050.1475925926</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216105</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46057.9737731482</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>46057.234375</x:v>
       </x:c>
-      <x:c r="I8" s="37">
+      <x:c r="I10" s="30">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J8" s="35" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1216128</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L8" s="36">
+      <x:c r="L10" s="32">
         <x:v>46072.0668055556</x:v>
       </x:c>
-      <x:c r="M8" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G9" s="35" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H9" s="36">
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>46066.1502662037</x:v>
       </x:c>
-      <x:c r="I9" s="37">
+      <x:c r="I11" s="30">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J9" s="35" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216135</x:v>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="36">
+      <x:c r="L11" s="32">
         <x:v>46077.9542708333</x:v>
       </x:c>
-      <x:c r="M9" s="35" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>46051.2882638889</x:v>
       </x:c>
-      <x:c r="I10" s="44">
+      <x:c r="I12" s="30">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1216104</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>46057.963587963</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="45" t="s"/>
-      <x:c r="C11" s="45" t="s"/>
-      <x:c r="D11" s="45" t="s"/>
-      <x:c r="E11" s="45" t="s"/>
-      <x:c r="F11" s="45" t="s"/>
-      <x:c r="G11" s="45" t="s"/>
-      <x:c r="H11" s="45" t="s"/>
-      <x:c r="I11" s="45" t="s"/>
-      <x:c r="J11" s="45" t="s"/>
-      <x:c r="K11" s="45" t="s"/>
-      <x:c r="L11" s="45" t="s"/>
-      <x:c r="M11" s="45" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="45" t="s"/>
-      <x:c r="C12" s="45" t="s"/>
-      <x:c r="D12" s="45" t="s"/>
-      <x:c r="E12" s="45" t="s"/>
-      <x:c r="F12" s="45" t="s"/>
-      <x:c r="G12" s="45" t="s"/>
-      <x:c r="H12" s="45" t="s"/>
-      <x:c r="I12" s="45" t="s"/>
-      <x:c r="J12" s="45" t="s"/>
-      <x:c r="K12" s="45" t="s"/>
-      <x:c r="L12" s="45" t="s"/>
-      <x:c r="M12" s="45" t="s"/>
+      <x:c r="M12" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
+      <x:c r="B15" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s"/>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="17" t="s"/>
+      <x:c r="F15" s="17" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
-        <x:v>10</x:v>
+      <x:c r="B16" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="20" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="21" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
+      <x:c r="B19" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1037,9 +1037,12 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1115,7 +1118,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1145,6 +1148,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1483,7 +1490,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1555,716 +1564,716 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46065.33125</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45700</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216139</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46084.1560763889</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46085.2764814815</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>44879</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216175</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1290</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46093.2000115741</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>46065.2288541667</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216140</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46084.1582175926</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>46085.3007986111</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>46386</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216177</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46093.215162037</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>46085.2858333333</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>46096</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1216176</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>46093.2057060185</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>46072.3153009259</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1216162</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>46090.311412037</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s">
+      <x:c r="C14" s="28" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s">
+      <x:c r="D14" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="27" t="s">
+      <x:c r="E14" s="28" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="F14" s="28" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G14" s="27" t="s">
+      <x:c r="G14" s="28" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="H14" s="29">
+      <x:c r="H14" s="30">
         <x:v>46073.0262847222</x:v>
       </x:c>
-      <x:c r="I14" s="30">
+      <x:c r="I14" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J14" s="28" t="n">
+      <x:c r="J14" s="29" t="n">
         <x:v>1216157</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L14" s="32">
+      <x:c r="L14" s="33">
         <x:v>46090.267025463</x:v>
       </x:c>
-      <x:c r="M14" s="27" t="s">
+      <x:c r="M14" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s">
+      <x:c r="C15" s="28" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s">
+      <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="27" t="s">
+      <x:c r="E15" s="28" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="F15" s="28" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G15" s="27" t="s">
+      <x:c r="G15" s="28" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H15" s="29">
+      <x:c r="H15" s="30">
         <x:v>46077.2103587963</x:v>
       </x:c>
-      <x:c r="I15" s="30">
+      <x:c r="I15" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J15" s="28" t="n">
+      <x:c r="J15" s="29" t="n">
         <x:v>1216155</x:v>
       </x:c>
-      <x:c r="K15" s="31" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L15" s="32">
+      <x:c r="L15" s="33">
         <x:v>46090.2536226852</x:v>
       </x:c>
-      <x:c r="M15" s="27" t="s">
+      <x:c r="M15" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s">
+      <x:c r="C16" s="28" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="D16" s="28" t="s">
+      <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="27" t="s">
+      <x:c r="E16" s="28" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F16" s="27" t="s">
+      <x:c r="F16" s="28" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G16" s="27" t="s">
+      <x:c r="G16" s="28" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="H16" s="29">
+      <x:c r="H16" s="30">
         <x:v>46073.0478472222</x:v>
       </x:c>
-      <x:c r="I16" s="30">
+      <x:c r="I16" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J16" s="28" t="n">
+      <x:c r="J16" s="29" t="n">
         <x:v>1216153</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="32">
+      <x:c r="L16" s="33">
         <x:v>46090.2431828704</x:v>
       </x:c>
-      <x:c r="M16" s="27" t="s">
+      <x:c r="M16" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s">
+      <x:c r="C17" s="28" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="D17" s="28" t="s">
+      <x:c r="D17" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="27" t="s">
+      <x:c r="E17" s="28" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F17" s="27" t="s">
+      <x:c r="F17" s="28" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G17" s="27" t="s">
+      <x:c r="G17" s="28" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="H17" s="29">
+      <x:c r="H17" s="30">
         <x:v>46073.1095023148</x:v>
       </x:c>
-      <x:c r="I17" s="30">
+      <x:c r="I17" s="31">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J17" s="28" t="n">
+      <x:c r="J17" s="29" t="n">
         <x:v>1216164</x:v>
       </x:c>
-      <x:c r="K17" s="31" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L17" s="32">
+      <x:c r="L17" s="33">
         <x:v>46091.121087963</x:v>
       </x:c>
-      <x:c r="M17" s="27" t="s">
+      <x:c r="M17" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s">
+      <x:c r="C18" s="28" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D18" s="28" t="s">
+      <x:c r="D18" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="27" t="s">
+      <x:c r="E18" s="28" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F18" s="27" t="s">
+      <x:c r="F18" s="28" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G18" s="27" t="s">
+      <x:c r="G18" s="28" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H18" s="29">
+      <x:c r="H18" s="30">
         <x:v>46073.061099537</x:v>
       </x:c>
-      <x:c r="I18" s="30">
+      <x:c r="I18" s="31">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J18" s="28" t="n">
+      <x:c r="J18" s="29" t="n">
         <x:v>1216151</x:v>
       </x:c>
-      <x:c r="K18" s="31" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L18" s="32">
+      <x:c r="L18" s="33">
         <x:v>46090.2266435185</x:v>
       </x:c>
-      <x:c r="M18" s="27" t="s">
+      <x:c r="M18" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="27" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s">
+      <x:c r="C19" s="28" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D19" s="28" t="s">
+      <x:c r="D19" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E19" s="27" t="s">
+      <x:c r="E19" s="28" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="F19" s="27" t="s">
+      <x:c r="F19" s="28" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G19" s="27" t="s">
+      <x:c r="G19" s="28" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="H19" s="29">
+      <x:c r="H19" s="30">
         <x:v>46077.2683564815</x:v>
       </x:c>
-      <x:c r="I19" s="30">
+      <x:c r="I19" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J19" s="28" t="n">
+      <x:c r="J19" s="29" t="n">
         <x:v>1216159</x:v>
       </x:c>
-      <x:c r="K19" s="31" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L19" s="32">
+      <x:c r="L19" s="33">
         <x:v>46090.2806018519</x:v>
       </x:c>
-      <x:c r="M19" s="27" t="s">
+      <x:c r="M19" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="27" t="s">
+      <x:c r="B20" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s">
+      <x:c r="C20" s="28" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="D20" s="28" t="s">
+      <x:c r="D20" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E20" s="27" t="s">
+      <x:c r="E20" s="28" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F20" s="27" t="s">
+      <x:c r="F20" s="28" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G20" s="27" t="s">
+      <x:c r="G20" s="28" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="H20" s="29">
+      <x:c r="H20" s="30">
         <x:v>46073.0763541667</x:v>
       </x:c>
-      <x:c r="I20" s="30">
+      <x:c r="I20" s="31">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J20" s="28" t="n">
+      <x:c r="J20" s="29" t="n">
         <x:v>1216149</x:v>
       </x:c>
-      <x:c r="K20" s="31" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L20" s="32">
+      <x:c r="L20" s="33">
         <x:v>46090.2162847222</x:v>
       </x:c>
-      <x:c r="M20" s="27" t="s">
+      <x:c r="M20" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="27" t="s">
+      <x:c r="B21" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s">
+      <x:c r="C21" s="28" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D21" s="28" t="s">
+      <x:c r="D21" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E21" s="27" t="s">
+      <x:c r="E21" s="28" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F21" s="27" t="s">
+      <x:c r="F21" s="28" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G21" s="27" t="s">
+      <x:c r="G21" s="28" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H21" s="29">
+      <x:c r="H21" s="30">
         <x:v>46077.1834259259</x:v>
       </x:c>
-      <x:c r="I21" s="30">
+      <x:c r="I21" s="31">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J21" s="28" t="n">
+      <x:c r="J21" s="29" t="n">
         <x:v>1216166</x:v>
       </x:c>
-      <x:c r="K21" s="31" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L21" s="32">
+      <x:c r="L21" s="33">
         <x:v>46091.2388773148</x:v>
       </x:c>
-      <x:c r="M21" s="27" t="s">
+      <x:c r="M21" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="27" t="s">
+      <x:c r="B22" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s">
+      <x:c r="C22" s="28" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D22" s="28" t="s">
+      <x:c r="D22" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E22" s="27" t="s">
+      <x:c r="E22" s="28" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F22" s="27" t="s">
+      <x:c r="F22" s="28" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G22" s="27" t="s">
+      <x:c r="G22" s="28" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H22" s="29">
+      <x:c r="H22" s="30">
         <x:v>46071.2853587963</x:v>
       </x:c>
-      <x:c r="I22" s="30">
+      <x:c r="I22" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J22" s="28" t="n">
+      <x:c r="J22" s="29" t="n">
         <x:v>1216191</x:v>
       </x:c>
-      <x:c r="K22" s="31" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L22" s="32">
+      <x:c r="L22" s="33">
         <x:v>46094.1777199074</x:v>
       </x:c>
-      <x:c r="M22" s="27" t="s">
+      <x:c r="M22" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="27" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s">
+      <x:c r="C23" s="28" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D23" s="28" t="s">
+      <x:c r="D23" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E23" s="27" t="s">
+      <x:c r="E23" s="28" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F23" s="27" t="s">
+      <x:c r="F23" s="28" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G23" s="27" t="s">
+      <x:c r="G23" s="28" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H23" s="29">
+      <x:c r="H23" s="30">
         <x:v>46090.3681365741</x:v>
       </x:c>
-      <x:c r="I23" s="30">
+      <x:c r="I23" s="31">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J23" s="28" t="n">
+      <x:c r="J23" s="29" t="n">
         <x:v>1216192</x:v>
       </x:c>
-      <x:c r="K23" s="31" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L23" s="32">
+      <x:c r="L23" s="33">
         <x:v>46094.182662037</x:v>
       </x:c>
-      <x:c r="M23" s="27" t="s">
+      <x:c r="M23" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="15" t="s">
+      <x:c r="B26" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C26" s="16" t="s"/>
-      <x:c r="D26" s="16" t="s"/>
-      <x:c r="E26" s="17" t="s"/>
-      <x:c r="F26" s="17" t="s"/>
+      <x:c r="C26" s="17" t="s"/>
+      <x:c r="D26" s="17" t="s"/>
+      <x:c r="E26" s="18" t="s"/>
+      <x:c r="F26" s="18" t="s"/>
     </x:row>
     <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="18" t="s">
+      <x:c r="B27" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C27" s="19" t="s"/>
-      <x:c r="D27" s="19" t="s"/>
-      <x:c r="E27" s="19" t="s"/>
-      <x:c r="F27" s="20" t="s">
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="20" t="s"/>
+      <x:c r="F27" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="21" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="23" t="n">
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="21" t="s">
+      <x:c r="B29" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C29" s="22" t="s"/>
-      <x:c r="D29" s="22" t="s"/>
-      <x:c r="E29" s="22" t="s"/>
-      <x:c r="F29" s="23" t="n">
+      <x:c r="C29" s="23" t="s"/>
+      <x:c r="D29" s="23" t="s"/>
+      <x:c r="E29" s="23" t="s"/>
+      <x:c r="F29" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="21" t="s">
+      <x:c r="B30" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C30" s="22" t="s"/>
-      <x:c r="D30" s="22" t="s"/>
-      <x:c r="E30" s="22" t="s"/>
-      <x:c r="F30" s="23" t="n">
+      <x:c r="C30" s="23" t="s"/>
+      <x:c r="D30" s="23" t="s"/>
+      <x:c r="E30" s="23" t="s"/>
+      <x:c r="F30" s="24" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="24" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="s"/>
-      <x:c r="D31" s="25" t="s"/>
-      <x:c r="E31" s="25" t="s"/>
-      <x:c r="F31" s="26" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -3301,7 +3310,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45839</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3373,80 +3384,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45861.181087963</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215835</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45862.1344560185</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -3466,44 +3477,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4555,7 +4566,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45870</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -4627,434 +4640,434 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45881.1074421296</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45889</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1195698</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45882.1141782407</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45881.2688541667</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1346458</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45882.0237847222</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45897.2409837963</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45681</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1346493</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45897.2777430556</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45875.2668402778</x:v>
       </x:c>
-      <x:c r="I11" s="29">
+      <x:c r="I11" s="30">
         <x:v>45875.2668518519</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1215854</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>45877.2327314815</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>45889.2616782407</x:v>
       </x:c>
-      <x:c r="I12" s="29">
+      <x:c r="I12" s="30">
         <x:v>45889.2616898148</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1215867</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>45891.1582986111</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>45889.1521064815</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>44272</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1215866</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>45891.153287037</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s">
+      <x:c r="C14" s="28" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s">
+      <x:c r="D14" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E14" s="27" t="s">
+      <x:c r="E14" s="28" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="F14" s="28" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G14" s="27" t="s">
+      <x:c r="G14" s="28" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H14" s="29">
+      <x:c r="H14" s="30">
         <x:v>45887.5499305556</x:v>
       </x:c>
-      <x:c r="I14" s="29">
+      <x:c r="I14" s="30">
         <x:v>45887.5499537037</x:v>
       </x:c>
-      <x:c r="J14" s="28" t="n">
+      <x:c r="J14" s="29" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L14" s="32">
+      <x:c r="L14" s="33">
         <x:v>45891.1027199074</x:v>
       </x:c>
-      <x:c r="M14" s="27" t="s">
+      <x:c r="M14" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s">
+      <x:c r="C15" s="28" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s">
+      <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="27" t="s">
+      <x:c r="E15" s="28" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="F15" s="28" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G15" s="27" t="s">
+      <x:c r="G15" s="28" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H15" s="29">
+      <x:c r="H15" s="30">
         <x:v>45883.2595717593</x:v>
       </x:c>
-      <x:c r="I15" s="30">
+      <x:c r="I15" s="31">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J15" s="28" t="n">
+      <x:c r="J15" s="29" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K15" s="31" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="32">
+      <x:c r="L15" s="33">
         <x:v>45883.2880208333</x:v>
       </x:c>
-      <x:c r="M15" s="27" t="s">
+      <x:c r="M15" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C18" s="16" t="s"/>
-      <x:c r="D18" s="16" t="s"/>
-      <x:c r="E18" s="17" t="s"/>
-      <x:c r="F18" s="17" t="s"/>
+      <x:c r="C18" s="17" t="s"/>
+      <x:c r="D18" s="17" t="s"/>
+      <x:c r="E18" s="18" t="s"/>
+      <x:c r="F18" s="18" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="18" t="s">
+      <x:c r="B19" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C19" s="19" t="s"/>
-      <x:c r="D19" s="19" t="s"/>
-      <x:c r="E19" s="19" t="s"/>
-      <x:c r="F19" s="20" t="s">
+      <x:c r="C19" s="20" t="s"/>
+      <x:c r="D19" s="20" t="s"/>
+      <x:c r="E19" s="20" t="s"/>
+      <x:c r="F19" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="21" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="n">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="21" t="s">
+      <x:c r="B23" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="23" t="n">
+      <x:c r="C23" s="23" t="s"/>
+      <x:c r="D23" s="23" t="s"/>
+      <x:c r="E23" s="23" t="s"/>
+      <x:c r="F23" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="21" t="s">
+      <x:c r="B24" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="22" t="s"/>
-      <x:c r="F24" s="23" t="n">
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="24" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C25" s="25" t="s"/>
-      <x:c r="D25" s="25" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="26" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6099,7 +6112,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45901</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -6171,336 +6186,336 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45902.1777546296</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45781</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215887</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45911.9486574074</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45887.2917592593</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215880</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45903.1177546296</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45911.4396296296</x:v>
       </x:c>
-      <x:c r="I10" s="29">
+      <x:c r="I10" s="30">
         <x:v>45911.4396296296</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1215899</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45918.0952083333</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45925.3972453704</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>47021</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1215915</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>45930.1169560185</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>45916.1769097222</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1215916</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>45930.1671643518</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>45912.47375</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1215898</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>45918.0905787037</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="s"/>
-      <x:c r="D16" s="16" t="s"/>
-      <x:c r="E16" s="17" t="s"/>
-      <x:c r="F16" s="17" t="s"/>
+      <x:c r="C16" s="17" t="s"/>
+      <x:c r="D16" s="17" t="s"/>
+      <x:c r="E16" s="18" t="s"/>
+      <x:c r="F16" s="18" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="18" t="s">
+      <x:c r="B17" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="19" t="s"/>
-      <x:c r="F17" s="20" t="s">
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="20" t="s"/>
+      <x:c r="F17" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="24" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7547,7 +7562,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45931</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -7619,173 +7636,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45938.0053703704</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215952</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45945.1196180556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45945.2727662037</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215958</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45953.151099537</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="C12" s="17" t="s"/>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="18" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8836,7 +8853,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45962</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -8908,287 +8927,287 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45944.1129282407</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215998</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45971.316400463</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45954.1265625</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45626</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215975</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45967.0018287037</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45965.2541435185</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1215995</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45971.1502199074</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45966.1203125</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216011</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>45975.3046180556</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>45966.1218055556</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1216012</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>45975.312349537</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="s"/>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="17" t="s"/>
-      <x:c r="F15" s="17" t="s"/>
+      <x:c r="C15" s="17" t="s"/>
+      <x:c r="D15" s="17" t="s"/>
+      <x:c r="E15" s="18" t="s"/>
+      <x:c r="F15" s="18" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="18" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="20" t="s">
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="24" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -10236,7 +10255,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45992</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -10308,162 +10329,162 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45979.0549768519</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216037</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46006.2690046296</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45972.2314236111</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216026</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45992.0065509259</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="C12" s="17" t="s"/>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="18" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -11514,7 +11535,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46023</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -11586,345 +11609,345 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46007.2920138889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46007.292037037</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1195956</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46044.2434953704</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46031.042974537</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46015</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216079</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46043.2977199074</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>46029.1168055556</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216071</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46036.0526736111</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>46029.112962963</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216072</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46036.0583564815</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>46036.929224537</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1216095</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>46050.0472337963</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>46034.1741087963</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1216082</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="s"/>
-      <x:c r="D16" s="16" t="s"/>
-      <x:c r="E16" s="17" t="s"/>
-      <x:c r="F16" s="17" t="s"/>
+      <x:c r="C16" s="17" t="s"/>
+      <x:c r="D16" s="17" t="s"/>
+      <x:c r="E16" s="18" t="s"/>
+      <x:c r="F16" s="18" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="18" t="s">
+      <x:c r="B17" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="19" t="s"/>
-      <x:c r="F17" s="20" t="s">
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="20" t="s"/>
+      <x:c r="F17" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -12971,7 +12994,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46054</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -13043,298 +13068,298 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46072.0406597222</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46077.0821759259</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1195996</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46078.028275463</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46050.1475925926</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45988</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216105</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46057.9737731482</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>46057.234375</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216128</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46072.0668055556</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>46066.1502662037</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216135</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46077.9542708333</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>46051.2882638889</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1216104</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>46057.963587963</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="s"/>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="17" t="s"/>
-      <x:c r="F15" s="17" t="s"/>
+      <x:c r="C15" s="17" t="s"/>
+      <x:c r="D15" s="17" t="s"/>
+      <x:c r="E15" s="18" t="s"/>
+      <x:c r="F15" s="18" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="18" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="20" t="s">
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="21" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,9 +30,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
-  <x:si>
-    <x:t>CERTIFICATE SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CERTIFICATES SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | July 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -104,6 +110,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -218,6 +227,9 @@
     <x:t>61-8-2025-1123</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | September 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARNEL REPOSAR CANDANO</x:t>
   </x:si>
   <x:si>
@@ -290,6 +302,9 @@
     <x:t>61-9-2025-1152</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | October 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN ALMENDRAL ALCORIZA</x:t>
   </x:si>
   <x:si>
@@ -314,6 +329,9 @@
     <x:t>61-10-2025-1194</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | November 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGAPITO PERATER BERALLO</x:t>
   </x:si>
   <x:si>
@@ -371,6 +389,9 @@
     <x:t>61-11-2025-1228</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | December 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRESENCIO CUA JUSAY</x:t>
   </x:si>
   <x:si>
@@ -395,6 +416,9 @@
     <x:t>61-11-2025-1237</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | January 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Certified True Copy</x:t>
   </x:si>
   <x:si>
@@ -470,6 +494,9 @@
     <x:t>61-1-2026-1273-054</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
@@ -531,6 +558,9 @@
   </x:si>
   <x:si>
     <x:t>61-1-2026-1302-574</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>FERNANDO B LAKAG</x:t>
@@ -726,7 +756,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -766,6 +796,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1037,15 +1091,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1060,55 +1120,10 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1117,8 +1132,53 @@
     <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1149,80 +1209,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1241,7 +1241,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1470,58 +1538,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1564,716 +1632,716 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46065.33125</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45700</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216139</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46084.1560763889</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46085.2764814815</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216175</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46093.2000115741</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46065.2288541667</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1216140</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>46084.1582175926</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46085.3007986111</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>46386</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1216177</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>46093.215162037</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46085.2858333333</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1216176</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>46093.2057060185</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46072.3153009259</x:v>
+      </x:c>
+      <x:c r="I13" s="33">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1216162</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L13" s="35">
+        <x:v>46090.311412037</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>46065.33125</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45700</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1216139</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>46084.1560763889</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="C14" s="30" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I14" s="33">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K14" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="35">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46085.2764814815</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1216175</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46093.2000115741</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="C15" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I15" s="33">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K15" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L15" s="35">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>46065.2288541667</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1216140</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46084.1582175926</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="C16" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I16" s="33">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K16" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L16" s="35">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>46085.3007986111</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46386</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1216177</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46093.215162037</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
+      <x:c r="C17" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46073.1095023148</x:v>
+      </x:c>
+      <x:c r="I17" s="33">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="n">
+        <x:v>1216164</x:v>
+      </x:c>
+      <x:c r="K17" s="34" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L17" s="35">
+        <x:v>46091.121087963</x:v>
+      </x:c>
+      <x:c r="M17" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>46085.2858333333</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>46096</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1216176</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>46093.2057060185</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
+      <x:c r="C18" s="30" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I18" s="33">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K18" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L18" s="35">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M18" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46072.3153009259</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1216162</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
+      <x:c r="C19" s="30" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I19" s="33">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K19" s="34" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L13" s="33">
-        <x:v>46090.311412037</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="s">
+      <x:c r="L19" s="35">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M19" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="28" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F14" s="28" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H14" s="30">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J14" s="29" t="n">
-        <x:v>1216157</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L14" s="33">
-        <x:v>46090.267025463</x:v>
-      </x:c>
-      <x:c r="M14" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D15" s="29" t="s">
+      <x:c r="C20" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I20" s="33">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K20" s="34" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="35">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M20" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="28" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="n">
-        <x:v>1216155</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L15" s="33">
-        <x:v>46090.2536226852</x:v>
-      </x:c>
-      <x:c r="M15" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="D16" s="29" t="s">
+      <x:c r="C21" s="30" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F21" s="30" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I21" s="33">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K21" s="34" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L21" s="35">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M21" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="28" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F16" s="28" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G16" s="28" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="n">
-        <x:v>1216153</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L16" s="33">
-        <x:v>46090.2431828704</x:v>
-      </x:c>
-      <x:c r="M16" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D17" s="29" t="s">
+      <x:c r="C22" s="30" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I22" s="33">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K22" s="34" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L22" s="35">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M22" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="28" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F17" s="28" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G17" s="28" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
-        <x:v>46073.1095023148</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J17" s="29" t="n">
-        <x:v>1216164</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L17" s="33">
-        <x:v>46091.121087963</x:v>
-      </x:c>
-      <x:c r="M17" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D18" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="28" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F18" s="28" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G18" s="28" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46073.061099537</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="n">
-        <x:v>1216151</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L18" s="33">
-        <x:v>46090.2266435185</x:v>
-      </x:c>
-      <x:c r="M18" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s">
+      <x:c r="C23" s="30" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I23" s="33">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K23" s="34" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D19" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="28" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F19" s="28" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G19" s="28" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H19" s="30">
-        <x:v>46077.2683564815</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J19" s="29" t="n">
-        <x:v>1216159</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L19" s="33">
-        <x:v>46090.2806018519</x:v>
-      </x:c>
-      <x:c r="M19" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D20" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="28" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F20" s="28" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G20" s="28" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H20" s="30">
-        <x:v>46073.0763541667</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J20" s="29" t="n">
-        <x:v>1216149</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L20" s="33">
-        <x:v>46090.2162847222</x:v>
-      </x:c>
-      <x:c r="M20" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D21" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="28" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F21" s="28" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G21" s="28" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46077.1834259259</x:v>
-      </x:c>
-      <x:c r="I21" s="31">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="n">
-        <x:v>1216166</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L21" s="33">
-        <x:v>46091.2388773148</x:v>
-      </x:c>
-      <x:c r="M21" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D22" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E22" s="28" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F22" s="28" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G22" s="28" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H22" s="30">
-        <x:v>46071.2853587963</x:v>
-      </x:c>
-      <x:c r="I22" s="31">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J22" s="29" t="n">
-        <x:v>1216191</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L22" s="33">
-        <x:v>46094.1777199074</x:v>
-      </x:c>
-      <x:c r="M22" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C23" s="28" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D23" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E23" s="28" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F23" s="28" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46090.3681365741</x:v>
-      </x:c>
-      <x:c r="I23" s="31">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="n">
-        <x:v>1216192</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L23" s="33">
+      <x:c r="L23" s="35">
         <x:v>46094.182662037</x:v>
       </x:c>
-      <x:c r="M23" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M23" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s"/>
-      <x:c r="D26" s="17" t="s"/>
-      <x:c r="E26" s="18" t="s"/>
-      <x:c r="F26" s="18" t="s"/>
+      <x:c r="B26" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C26" s="19" t="s"/>
+      <x:c r="D26" s="19" t="s"/>
+      <x:c r="E26" s="20" t="s"/>
+      <x:c r="F26" s="20" t="s"/>
     </x:row>
     <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C27" s="20" t="s"/>
-      <x:c r="D27" s="20" t="s"/>
-      <x:c r="E27" s="20" t="s"/>
-      <x:c r="F27" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B27" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="n">
+      <x:c r="B28" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C29" s="23" t="s"/>
-      <x:c r="D29" s="23" t="s"/>
-      <x:c r="E29" s="23" t="s"/>
-      <x:c r="F29" s="24" t="n">
+      <x:c r="B29" s="24" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C30" s="23" t="s"/>
-      <x:c r="D30" s="23" t="s"/>
-      <x:c r="E30" s="23" t="s"/>
-      <x:c r="F30" s="24" t="n">
+      <x:c r="B30" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
+      <x:c r="B31" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -3243,7 +3311,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B26:F26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
@@ -3290,58 +3358,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3384,81 +3452,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45861.181087963</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215835</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45862.1344560185</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3477,44 +3545,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4501,7 +4569,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -4546,58 +4614,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45870</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -4640,434 +4708,434 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45881.1074421296</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45889</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1195698</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45882.1141782407</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45881.2688541667</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346458</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45882.0237847222</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>45875.2668402778</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>45875.2668518519</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1215854</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>45877.2327314815</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45889.2616782407</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>45889.2616898148</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1215867</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>45891.1582986111</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>45889.1521064815</x:v>
+      </x:c>
+      <x:c r="I13" s="33">
+        <x:v>44272</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1215866</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L13" s="35">
+        <x:v>45891.153287037</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>45887.5499305556</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>45887.5499537037</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K14" s="34" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L14" s="35">
+        <x:v>45891.1027199074</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45881.1074421296</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45889</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1195698</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45882.1141782407</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
+      <x:c r="C15" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>45883.2595717593</x:v>
+      </x:c>
+      <x:c r="I15" s="33">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K15" s="34" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="L15" s="35">
+        <x:v>45883.2880208333</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>45875.2668402778</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45875.2668518519</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1215854</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45877.2327314815</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>45889.2616782407</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1215867</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45891.1582986111</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>45889.1521064815</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>44272</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1215866</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45891.153287037</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E14" s="28" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F14" s="28" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H14" s="30">
-        <x:v>45887.5499305556</x:v>
-      </x:c>
-      <x:c r="I14" s="30">
-        <x:v>45887.5499537037</x:v>
-      </x:c>
-      <x:c r="J14" s="29" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L14" s="33">
-        <x:v>45891.1027199074</x:v>
-      </x:c>
-      <x:c r="M14" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D15" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>45883.2595717593</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="L15" s="33">
-        <x:v>45883.2880208333</x:v>
-      </x:c>
-      <x:c r="M15" s="28" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s"/>
-      <x:c r="D18" s="17" t="s"/>
-      <x:c r="E18" s="18" t="s"/>
-      <x:c r="F18" s="18" t="s"/>
+      <x:c r="B18" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C18" s="19" t="s"/>
+      <x:c r="D18" s="19" t="s"/>
+      <x:c r="E18" s="20" t="s"/>
+      <x:c r="F18" s="20" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C19" s="20" t="s"/>
-      <x:c r="D19" s="20" t="s"/>
-      <x:c r="E19" s="20" t="s"/>
-      <x:c r="F19" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B19" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="n">
+      <x:c r="B21" s="24" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="n">
+      <x:c r="B22" s="24" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s"/>
-      <x:c r="D23" s="23" t="s"/>
-      <x:c r="E23" s="23" t="s"/>
-      <x:c r="F23" s="24" t="n">
+      <x:c r="B23" s="24" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s"/>
-      <x:c r="D24" s="23" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="24" t="n">
+      <x:c r="B24" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
+      <x:c r="B25" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6043,7 +6111,7 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
@@ -6092,58 +6160,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45901</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -6186,336 +6254,336 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45902.1777546296</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45781</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215887</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45911.9486574074</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45887.2917592593</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215880</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45903.1177546296</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1215899</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>45918.0952083333</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45902.1777546296</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45781</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1215887</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45911.9486574074</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="C11" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>45925.3972453704</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>47021</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1215915</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>45930.1169560185</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1215899</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45918.0952083333</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="C12" s="30" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45916.1769097222</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1215916</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>45930.1671643518</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>45925.3972453704</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>47021</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1215915</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45930.1169560185</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>45916.1769097222</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1215916</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45930.1671643518</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
+      <x:c r="C13" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
         <x:v>45912.47375</x:v>
       </x:c>
-      <x:c r="I13" s="31">
+      <x:c r="I13" s="33">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J13" s="29" t="n">
+      <x:c r="J13" s="31" t="n">
         <x:v>1215898</x:v>
       </x:c>
-      <x:c r="K13" s="32" t="n">
+      <x:c r="K13" s="34" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="33">
+      <x:c r="L13" s="35">
         <x:v>45918.0905787037</x:v>
       </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s"/>
-      <x:c r="D16" s="17" t="s"/>
-      <x:c r="E16" s="18" t="s"/>
-      <x:c r="F16" s="18" t="s"/>
+      <x:c r="B16" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="20" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="20" t="s"/>
-      <x:c r="D17" s="20" t="s"/>
-      <x:c r="E17" s="20" t="s"/>
-      <x:c r="F17" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B17" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
+      <x:c r="B21" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7495,7 +7563,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
@@ -7542,58 +7610,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45931</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -7636,173 +7704,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45938.0053703704</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215952</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45945.1196180556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45938.0053703704</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1215952</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45945.1196180556</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45945.2727662037</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215958</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45953.151099537</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s"/>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="18" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B13" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8787,7 +8855,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -8833,58 +8901,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45962</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -8927,287 +8995,287 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45944.1129282407</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215998</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45971.316400463</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45954.1265625</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45626</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215975</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45967.0018287037</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45965.2541435185</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>45971</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1215995</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>45971.1502199074</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="C11" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>45966.1203125</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1216011</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>45975.3046180556</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45954.1265625</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45626</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1215975</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45967.0018287037</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>45965.2541435185</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45971</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1215995</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="C12" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45966.1218055556</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1216012</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45971.1502199074</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>45966.1203125</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1216011</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45975.3046180556</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>45966.1218055556</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1216012</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
+      <x:c r="L12" s="35">
         <x:v>45975.312349537</x:v>
       </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s"/>
-      <x:c r="D15" s="17" t="s"/>
-      <x:c r="E15" s="18" t="s"/>
-      <x:c r="F15" s="18" t="s"/>
+      <x:c r="B15" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="20" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="20" t="s"/>
-      <x:c r="F16" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B16" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="B19" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -10189,7 +10257,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
@@ -10235,58 +10303,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -10329,162 +10397,162 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45979.0549768519</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216037</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46006.2690046296</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45972.2314236111</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216026</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45992.0065509259</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s"/>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="18" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B13" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -11470,7 +11538,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -11515,58 +11583,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -11609,345 +11677,345 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="B8" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46007.2920138889</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46007.292037037</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1195956</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46044.2434953704</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>126</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46031.042974537</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216079</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46043.2977199074</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46029.1168055556</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1216071</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>46036.0526736111</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="C11" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46029.112962963</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1216072</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>46036.0583564815</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46036.0526736111</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="C12" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46036.929224537</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1216095</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>46050.0472337963</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>46029.112962963</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1216072</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="C13" s="30" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46034.1741087963</x:v>
+      </x:c>
+      <x:c r="I13" s="33">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1216082</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46036.0583564815</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>46036.929224537</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1216095</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>46050.0472337963</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
+      <x:c r="L13" s="35">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s"/>
-      <x:c r="D16" s="17" t="s"/>
-      <x:c r="E16" s="18" t="s"/>
-      <x:c r="F16" s="18" t="s"/>
+      <x:c r="B16" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="20" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="20" t="s"/>
-      <x:c r="D17" s="20" t="s"/>
-      <x:c r="E17" s="20" t="s"/>
-      <x:c r="F17" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B17" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="n">
+      <x:c r="B21" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
+      <x:c r="B22" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -12926,7 +12994,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
@@ -12974,58 +13042,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -13068,298 +13136,298 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="B8" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46072.0406597222</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46077.0821759259</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1195996</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46078.028275463</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>126</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46050.1475925926</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216105</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46057.9737731482</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46057.234375</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1216128</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>46072.0668055556</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46066.1502662037</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1216135</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>46077.9542708333</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>46057.234375</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1216128</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46072.0668055556</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>46066.1502662037</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1216135</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46077.9542708333</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
+      <x:c r="C12" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
         <x:v>46051.2882638889</x:v>
       </x:c>
-      <x:c r="I12" s="31">
+      <x:c r="I12" s="33">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J12" s="29" t="n">
+      <x:c r="J12" s="31" t="n">
         <x:v>1216104</x:v>
       </x:c>
-      <x:c r="K12" s="32" t="n">
+      <x:c r="K12" s="34" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L12" s="33">
+      <x:c r="L12" s="35">
         <x:v>46057.963587963</x:v>
       </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s"/>
-      <x:c r="D15" s="17" t="s"/>
-      <x:c r="E15" s="18" t="s"/>
-      <x:c r="F15" s="18" t="s"/>
+      <x:c r="B15" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="20" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="20" t="s"/>
-      <x:c r="F16" s="21" t="s">
-        <x:v>22</x:v>
+      <x:c r="B16" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
+      <x:c r="B20" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -14340,7 +14408,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -75,42 +75,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Special Radio Operator Certificate (RENEWAL)</x:t>
@@ -794,7 +758,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -838,14 +802,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -860,10 +816,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -878,6 +842,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -1114,7 +1085,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1122,16 +1093,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1143,13 +1114,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1159,6 +1124,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1179,10 +1147,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1194,8 +1165,14 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1226,28 +1203,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1260,10 +1229,6 @@
     </x:xf>
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1290,15 +1255,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1312,6 +1277,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1610,7 +1595,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>188</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -1643,7 +1628,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1683,733 +1668,683 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46065.33125</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45700</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216139</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46084.1560763889</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46085.2764814815</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216175</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46093.2000115741</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>46065.2288541667</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1216140</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>46084.1582175926</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>46085.3007986111</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>46386</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1216177</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>46093.215162037</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>46085.2858333333</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1216176</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>46093.2057060185</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H13" s="31">
+        <x:v>46072.3153009259</x:v>
+      </x:c>
+      <x:c r="I13" s="31">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="n">
+        <x:v>1216162</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L13" s="33">
+        <x:v>46090.311412037</x:v>
+      </x:c>
+      <x:c r="M13" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C14" s="29" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D14" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E14" s="29" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F14" s="29" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G14" s="29" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H14" s="31">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I14" s="31">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K14" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="33">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D15" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="29" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F15" s="29" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G15" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H15" s="31">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I15" s="31">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J15" s="30" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K15" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L15" s="33">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M15" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D16" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="29" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F16" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G16" s="29" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H16" s="31">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I16" s="31">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J16" s="30" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K16" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L16" s="33">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M16" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D17" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F17" s="29" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G17" s="29" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H17" s="31">
+        <x:v>46073.1095023148</x:v>
+      </x:c>
+      <x:c r="I17" s="31">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J17" s="30" t="n">
+        <x:v>1216164</x:v>
+      </x:c>
+      <x:c r="K17" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L17" s="33">
+        <x:v>46091.121087963</x:v>
+      </x:c>
+      <x:c r="M17" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D18" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F18" s="29" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H18" s="31">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I18" s="31">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K18" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L18" s="33">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M18" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D19" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="29" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F19" s="29" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H19" s="31">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I19" s="31">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J19" s="30" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K19" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L19" s="33">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M19" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D20" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F20" s="29" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H20" s="31">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I20" s="31">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K20" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="33">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M20" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D21" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="29" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F21" s="29" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G21" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H21" s="31">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I21" s="31">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J21" s="30" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K21" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L21" s="33">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M21" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D22" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="29" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F22" s="29" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G22" s="29" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H22" s="31">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I22" s="31">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J22" s="30" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K22" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L22" s="33">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M22" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D23" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="29" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F23" s="29" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G23" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H23" s="31">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I23" s="31">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K23" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L23" s="33">
+        <x:v>46094.182662037</x:v>
+      </x:c>
+      <x:c r="M23" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C26" s="18" t="s"/>
+      <x:c r="D26" s="18" t="s"/>
+      <x:c r="E26" s="19" t="s"/>
+      <x:c r="F26" s="19" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C27" s="21" t="s"/>
+      <x:c r="D27" s="21" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46065.33125</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45700</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216139</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46084.1560763889</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46085.2764814815</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216175</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46093.2000115741</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46065.2288541667</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216140</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46084.1582175926</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46085.3007986111</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46386</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216177</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46093.215162037</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46085.2858333333</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46096</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216176</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46093.2057060185</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46072.3153009259</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1216162</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46090.311412037</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1216157</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46090.267025463</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1216155</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46090.2536226852</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1216153</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46090.2431828704</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46073.1095023148</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1216164</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46091.121087963</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46073.061099537</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1216151</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46090.2266435185</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46077.2683564815</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1216159</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46090.2806018519</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46073.0763541667</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1216149</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46090.2162847222</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46077.1834259259</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1216166</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46091.2388773148</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46071.2853587963</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1216191</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46094.1777199074</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46090.3681365741</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1216192</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46094.182662037</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="22" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="C28" s="24" t="s"/>
+      <x:c r="D28" s="24" t="s"/>
+      <x:c r="E28" s="24" t="s"/>
+      <x:c r="F28" s="25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="23" t="s">
-        <x:v>35</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="24" t="s"/>
       <x:c r="D29" s="24" t="s"/>
       <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="F29" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C30" s="24" t="s"/>
+      <x:c r="D30" s="24" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="25" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="28" customHeight="1">
       <x:c r="B31" s="26" t="s">
-        <x:v>64</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C31" s="27" t="s"/>
       <x:c r="D31" s="27" t="s"/>
       <x:c r="E31" s="27" t="s"/>
       <x:c r="F31" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C33" s="30" t="s"/>
-      <x:c r="D33" s="30" t="s"/>
-      <x:c r="E33" s="30" t="s"/>
-      <x:c r="F33" s="31" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3376,12 +3311,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B28:F28"/>
+    <x:mergeCell ref="B26:F26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3526,7 +3461,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3566,141 +3501,104 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45861.181087963</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215835</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45862.1344560185</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45861.181087963</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1215835</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45862.1344560185</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4684,10 +4582,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4799,7 +4697,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4832,7 +4730,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4872,451 +4770,401 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45881.1074421296</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45889</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1195698</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45882.1141782407</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45881.2688541667</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346458</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45882.0237847222</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>45875.2668402778</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>45875.2668518519</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1215854</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>45877.2327314815</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>45889.2616782407</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>45889.2616898148</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1215867</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>45891.1582986111</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H13" s="31">
+        <x:v>45889.1521064815</x:v>
+      </x:c>
+      <x:c r="I13" s="31">
+        <x:v>44272</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="n">
+        <x:v>1215866</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L13" s="33">
+        <x:v>45891.153287037</x:v>
+      </x:c>
+      <x:c r="M13" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="29" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D14" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E14" s="29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F14" s="29" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G14" s="29" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H14" s="31">
+        <x:v>45887.5499305556</x:v>
+      </x:c>
+      <x:c r="I14" s="31">
+        <x:v>45887.5499537037</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K14" s="32" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L14" s="33">
+        <x:v>45891.1027199074</x:v>
+      </x:c>
+      <x:c r="M14" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C15" s="29" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D15" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="E15" s="29" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F15" s="29" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G15" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H15" s="31">
+        <x:v>45883.2595717593</x:v>
+      </x:c>
+      <x:c r="I15" s="31">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J15" s="30" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K15" s="32" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="L15" s="33">
+        <x:v>45883.2880208333</x:v>
+      </x:c>
+      <x:c r="M15" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C18" s="18" t="s"/>
+      <x:c r="D18" s="18" t="s"/>
+      <x:c r="E18" s="19" t="s"/>
+      <x:c r="F18" s="19" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="23" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45881.1074421296</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45889</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1195698</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45882.1141782407</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45875.2668402778</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45875.2668518519</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1215854</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45877.2327314815</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45889.2616782407</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1215867</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45891.1582986111</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45889.1521064815</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>44272</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1215866</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45891.153287037</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>45887.5499305556</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>45887.5499537037</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>45891.1027199074</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>45883.2595717593</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>45883.2880208333</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="24" t="s"/>
       <x:c r="D21" s="24" t="s"/>
       <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="F21" s="25" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>3</x:v>
+      <x:c r="B22" s="23" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="24" t="s"/>
+      <x:c r="F22" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>2</x:v>
+      <x:c r="B23" s="23" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C23" s="24" t="s"/>
+      <x:c r="D23" s="24" t="s"/>
+      <x:c r="E23" s="24" t="s"/>
+      <x:c r="F23" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="B24" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C24" s="24" t="s"/>
+      <x:c r="D24" s="24" t="s"/>
+      <x:c r="E24" s="24" t="s"/>
+      <x:c r="F24" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
       <x:c r="B25" s="26" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C25" s="27" t="s"/>
       <x:c r="D25" s="27" t="s"/>
       <x:c r="E25" s="27" t="s"/>
       <x:c r="F25" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6289,14 +6137,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
+    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -6408,7 +6256,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6441,7 +6289,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -6481,353 +6329,303 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45902.1777546296</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45781</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215887</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45911.9486574074</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45887.2917592593</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215880</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45903.1177546296</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1215899</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>45918.0952083333</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C11" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E11" s="29" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>45925.3972453704</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>47021</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1215915</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>45930.1169560185</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>45916.1769097222</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1215916</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>45930.1671643518</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H13" s="31">
+        <x:v>45912.47375</x:v>
+      </x:c>
+      <x:c r="I13" s="31">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="n">
+        <x:v>1215898</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L13" s="33">
+        <x:v>45918.0905787037</x:v>
+      </x:c>
+      <x:c r="M13" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C16" s="18" t="s"/>
+      <x:c r="D16" s="18" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="19" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45902.1777546296</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45781</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1215887</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45911.9486574074</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="23" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1215899</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45918.0952083333</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45925.3972453704</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>47021</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1215915</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45930.1169560185</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45916.1769097222</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1215916</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45930.1671643518</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45912.47375</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1215898</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45918.0905787037</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="24" t="s"/>
       <x:c r="D19" s="24" t="s"/>
       <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="F19" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
       <x:c r="E21" s="27" t="s"/>
       <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7804,12 +7602,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -7921,7 +7719,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -7954,7 +7752,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -7994,190 +7792,140 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45938.0053703704</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215952</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45945.1196180556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C9" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45945.2727662037</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45911</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215958</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45953.151099537</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45938.0053703704</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1215952</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45945.1196180556</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45945.2727662037</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45911</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1215958</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45953.151099537</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="23" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="24" t="s"/>
       <x:c r="D15" s="24" t="s"/>
       <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="F15" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
       <x:c r="E16" s="27" t="s"/>
       <x:c r="F16" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -9159,11 +8907,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -9275,7 +9023,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -9308,7 +9056,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -9348,304 +9096,254 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45944.1129282407</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215998</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45971.316400463</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45954.1265625</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45626</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215975</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45967.0018287037</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>45965.2541435185</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>45971</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1215995</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>45971.1502199074</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C11" s="29" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E11" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>45966.1203125</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1216011</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>45975.3046180556</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>45966.1218055556</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1216012</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>45975.312349537</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C15" s="18" t="s"/>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="19" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45954.1265625</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45626</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1215975</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45967.0018287037</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45965.2541435185</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45971</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1215995</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45971.1502199074</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45966.1203125</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216011</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45975.3046180556</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45966.1218055556</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216012</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45975.312349537</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="23" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="24" t="s"/>
       <x:c r="D18" s="24" t="s"/>
       <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="F18" s="25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
       <x:c r="E19" s="27" t="s"/>
       <x:c r="F19" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10624,11 +10322,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B17:F17"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -10740,7 +10438,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -10773,7 +10471,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -10813,179 +10511,129 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45979.0549768519</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46006.2690046296</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45972.2314236111</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216026</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45992.0065509259</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45979.0549768519</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46006.2690046296</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45972.2314236111</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216026</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45992.0065509259</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -11968,10 +11616,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -12083,7 +11731,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -12116,7 +11764,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -12156,362 +11804,312 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46007.2920138889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46007.292037037</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1195956</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46044.2434953704</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46031.042974537</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216079</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46043.2977199074</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>46029.1168055556</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1216071</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>46036.0526736111</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C11" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E11" s="29" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>46029.112962963</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1216072</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>46036.0583564815</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>46036.929224537</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1216095</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>46050.0472337963</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H13" s="31">
+        <x:v>46034.1741087963</x:v>
+      </x:c>
+      <x:c r="I13" s="31">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="n">
+        <x:v>1216082</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L13" s="33">
+        <x:v>46044.2691666667</x:v>
+      </x:c>
+      <x:c r="M13" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C16" s="18" t="s"/>
+      <x:c r="D16" s="18" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="19" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46007.2920138889</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46007.292037037</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1195956</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46044.2434953704</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46036.0526736111</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="23" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46029.112962963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216072</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46036.0583564815</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46036.929224537</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216095</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46050.0472337963</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46044.2691666667</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="24" t="s"/>
       <x:c r="D19" s="24" t="s"/>
       <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="F19" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="23" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>64</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -13487,13 +13085,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -13605,7 +13203,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -13638,7 +13236,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -13678,315 +13276,265 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46072.0406597222</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46077.0821759259</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1195996</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46078.028275463</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46050.1475925926</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216105</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46057.9737731482</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>46057.234375</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1216128</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>46072.0668055556</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>46066.1502662037</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1216135</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>46077.9542708333</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C12" s="29" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E12" s="29" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>46051.2882638889</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>44445</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1216104</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>46057.963587963</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C15" s="18" t="s"/>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="19" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46072.0406597222</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46077.0821759259</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1195996</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46078.028275463</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46057.234375</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216128</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46072.0668055556</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46066.1502662037</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216135</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46077.9542708333</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="23" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46051.2882638889</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>44445</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216104</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46057.963587963</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="C18" s="24" t="s"/>
       <x:c r="D18" s="24" t="s"/>
       <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="F18" s="25" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="B19" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
       <x:c r="E20" s="27" t="s"/>
       <x:c r="F20" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14964,12 +14512,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B17:F17"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -419,97 +419,82 @@
     <x:t>IX | January 2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Certified True Copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOSEPH GEORGE QUEZON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>V.C.H. Block. 29, Lot.44 Mahogany, Obay, Polanco, Zamboanga Del Norte</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIX-04182-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-12-2025-1261-872</x:t>
+    <x:t>MARENIE CAJETAS FLORA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P.Rubia, Buenavista, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96.1PX-16430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1269-970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDILBERTO ZUALSOLA TIGUELO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUROK MADANIHON 0792 G. LLUCH STREET, BALANGASAN, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLM-II-10399-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1268-653</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cashier 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93-GOVIX-047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1267-387</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARDION QUIZO DOMINGUEZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUBO- PAIT, Dumalinao, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22-SROPIX-13852</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1277-866</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAUL GALLEGO DIANAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK ORCHIDS, BOMBA, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21-SROPIX-13845</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1273-054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULITO SALDON ESPINAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None E.Aguinaldo, Ramon Magsaysay, Sindangan, Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1PHN-IX-06227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1341-726</x:t>
   </x:si>
   <x:si>
     <x:t>Fortunata Postigo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARENIE CAJETAS FLORA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P.Rubia, Buenavista, Pagadian City (Capital), Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.1PX-16430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1269-970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDILBERTO ZUALSOLA TIGUELO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUROK MADANIHON 0792 G. LLUCH STREET, BALANGASAN, Pagadian City (Capital), Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RLM-II-10399-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1268-653</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cashier 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93-GOVIX-047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1267-387</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARDION QUIZO DOMINGUEZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUBO- PAIT, Dumalinao, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22-SROPIX-13852</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1277-866</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAUL GALLEGO DIANAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A PUROK ORCHIDS, BOMBA, Pagadian City (Capital), Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21-SROPIX-13845</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1273-054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | February 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULITO SALDON ESPINAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None E.Aguinaldo, Ramon Magsaysay, Sindangan, Zamboanga Del Norte</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1PHN-IX-06227</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1341-726</x:t>
   </x:si>
   <x:si>
     <x:t>EMELIO LUZON PANOY</x:t>
@@ -1595,7 +1580,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>176</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -1674,19 +1659,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>178</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>46065.33125</x:v>
@@ -1712,19 +1697,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46085.2764814815</x:v>
@@ -1750,19 +1735,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H10" s="31">
         <x:v>46065.2288541667</x:v>
@@ -1788,19 +1773,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H11" s="31">
         <x:v>46085.3007986111</x:v>
@@ -1826,19 +1811,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>193</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H12" s="31">
         <x:v>46085.2858333333</x:v>
@@ -1864,19 +1849,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>199</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H13" s="31">
         <x:v>46072.3153009259</x:v>
@@ -1902,19 +1887,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>204</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H14" s="31">
         <x:v>46073.0262847222</x:v>
@@ -1940,19 +1925,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G15" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H15" s="31">
         <x:v>46077.2103587963</x:v>
@@ -1978,19 +1963,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D16" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F16" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G16" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H16" s="31">
         <x:v>46073.0478472222</x:v>
@@ -2016,19 +2001,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D17" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E17" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F17" s="29" t="s">
-        <x:v>215</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G17" s="29" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H17" s="31">
         <x:v>46073.1095023148</x:v>
@@ -2054,19 +2039,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D18" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="29" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F18" s="29" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="F18" s="29" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G18" s="29" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="H18" s="31">
         <x:v>46073.061099537</x:v>
@@ -2092,19 +2077,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C19" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D19" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G19" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H19" s="31">
         <x:v>46077.2683564815</x:v>
@@ -2130,19 +2115,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D20" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E20" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G20" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H20" s="31">
         <x:v>46073.0763541667</x:v>
@@ -2168,19 +2153,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D21" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
-        <x:v>229</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G21" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H21" s="31">
         <x:v>46077.1834259259</x:v>
@@ -2206,19 +2191,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>232</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>234</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H22" s="31">
         <x:v>46071.2853587963</x:v>
@@ -2244,19 +2229,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>235</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D23" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E23" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>237</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>238</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H23" s="31">
         <x:v>46090.3681365741</x:v>
@@ -11807,114 +11792,116 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
       <x:c r="H8" s="15">
-        <x:v>46007.2920138889</x:v>
+        <x:v>46031.042974537</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46007.292037037</x:v>
+        <x:v>46015</x:v>
       </x:c>
       <x:c r="J8" s="14" t="n">
-        <x:v>1195956</x:v>
+        <x:v>1216079</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
-        <x:v>54</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46044.2434953704</x:v>
+        <x:v>46043.2977199074</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46029.1168055556</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216071</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46036.0526736111</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46029.1168055556</x:v>
+        <x:v>46029.112962963</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>45778</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="J10" s="30" t="n">
-        <x:v>1216071</x:v>
+        <x:v>1216072</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46036.0526736111</x:v>
+        <x:v>46036.0583564815</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -11922,37 +11909,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46029.112962963</x:v>
+        <x:v>46036.929224537</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>45999</x:v>
+        <x:v>46053</x:v>
       </x:c>
       <x:c r="J11" s="30" t="n">
-        <x:v>1216072</x:v>
+        <x:v>1216095</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46036.0583564815</x:v>
+        <x:v>46050.0472337963</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -11960,102 +11947,75 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>149</x:v>
-      </x:c>
       <x:c r="H12" s="31">
-        <x:v>46036.929224537</x:v>
+        <x:v>46034.1741087963</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46053</x:v>
+        <x:v>45944</x:v>
       </x:c>
       <x:c r="J12" s="30" t="n">
-        <x:v>1216095</x:v>
+        <x:v>1216082</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
-        <x:v>90</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46050.0472337963</x:v>
+        <x:v>46044.2691666667</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>46044.2691666667</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="17" t="s">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C16" s="18" t="s"/>
-      <x:c r="D16" s="18" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="19" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="20" t="s">
+      <x:c r="C15" s="18" t="s"/>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="19" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="21" t="s"/>
-      <x:c r="F17" s="22" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="22" t="s">
         <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="23" t="s">
-        <x:v>129</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="24" t="s"/>
       <x:c r="D18" s="24" t="s"/>
@@ -12066,48 +12026,28 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C19" s="24" t="s"/>
       <x:c r="D19" s="24" t="s"/>
       <x:c r="E19" s="24" t="s"/>
       <x:c r="F19" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -13080,18 +13020,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -13203,7 +13142,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -13279,22 +13218,22 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>156</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>157</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>158</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>159</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>46072.0406597222</x:v>
@@ -13312,7 +13251,7 @@
         <x:v>46078.028275463</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -13320,19 +13259,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>160</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>161</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>163</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46050.1475925926</x:v>
@@ -13358,19 +13297,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H10" s="31">
         <x:v>46057.234375</x:v>
@@ -13396,19 +13335,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H11" s="31">
         <x:v>46066.1502662037</x:v>
@@ -13434,19 +13373,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H12" s="31">
         <x:v>46051.2882638889</x:v>
@@ -13491,7 +13430,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="23" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C17" s="24" t="s"/>
       <x:c r="D17" s="24" t="s"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -95,6 +95,9 @@
     <x:t>61-7-2025-1076</x:t>
   </x:si>
   <x:si>
+    <x:t>1215835</x:t>
+  </x:si>
+  <x:si>
     <x:t>Catalina EBON</x:t>
   </x:si>
   <x:si>
@@ -128,6 +131,9 @@
     <x:t>61-8-2025-1110</x:t>
   </x:si>
   <x:si>
+    <x:t>1195698</x:t>
+  </x:si>
+  <x:si>
     <x:t>Alexander Tomales</x:t>
   </x:si>
   <x:si>
@@ -143,6 +149,9 @@
     <x:t>61-8-2025-1112</x:t>
   </x:si>
   <x:si>
+    <x:t>1346458</x:t>
+  </x:si>
+  <x:si>
     <x:t>Neil Jon Angeles</x:t>
   </x:si>
   <x:si>
@@ -158,6 +167,9 @@
     <x:t>61-8-2025-1139</x:t>
   </x:si>
   <x:si>
+    <x:t>1346493</x:t>
+  </x:si>
+  <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
   </x:si>
   <x:si>
@@ -176,6 +188,9 @@
     <x:t>61-8-2025-1094</x:t>
   </x:si>
   <x:si>
+    <x:t>1215854</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARK FLOR</x:t>
   </x:si>
   <x:si>
@@ -188,6 +203,9 @@
     <x:t>61-8-2025-1136</x:t>
   </x:si>
   <x:si>
+    <x:t>1215867</x:t>
+  </x:si>
+  <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -200,6 +218,9 @@
     <x:t>61-8-2025-1135</x:t>
   </x:si>
   <x:si>
+    <x:t>1215866</x:t>
+  </x:si>
+  <x:si>
     <x:t>Special Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
@@ -215,6 +236,9 @@
     <x:t>61-8-2025-1128</x:t>
   </x:si>
   <x:si>
+    <x:t>1215865</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARDIANO NATIVIDAD BAYAWA</x:t>
   </x:si>
   <x:si>
@@ -227,6 +251,9 @@
     <x:t>61-8-2025-1123</x:t>
   </x:si>
   <x:si>
+    <x:t>1346470</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | September 2025</x:t>
   </x:si>
   <x:si>
@@ -242,6 +269,9 @@
     <x:t>61-9-2025-1142</x:t>
   </x:si>
   <x:si>
+    <x:t>1215887</x:t>
+  </x:si>
+  <x:si>
     <x:t>RONEL ESIC BACORRO</x:t>
   </x:si>
   <x:si>
@@ -254,6 +284,9 @@
     <x:t>61-8-2025-1127</x:t>
   </x:si>
   <x:si>
+    <x:t>1215880</x:t>
+  </x:si>
+  <x:si>
     <x:t>JENNY CULTURA CONTINEDO</x:t>
   </x:si>
   <x:si>
@@ -266,6 +299,9 @@
     <x:t>61-9-2025-1150</x:t>
   </x:si>
   <x:si>
+    <x:t>1215899</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARNOLD DECIERDO YATOR</x:t>
   </x:si>
   <x:si>
@@ -278,6 +314,9 @@
     <x:t>61-9-2025-1177</x:t>
   </x:si>
   <x:si>
+    <x:t>1215915</x:t>
+  </x:si>
+  <x:si>
     <x:t>NOEL HEPE RENIT</x:t>
   </x:si>
   <x:si>
@@ -290,6 +329,9 @@
     <x:t>61-9-2025-1161</x:t>
   </x:si>
   <x:si>
+    <x:t>1215916</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROCKIE SANCHEZ CORTINA</x:t>
   </x:si>
   <x:si>
@@ -302,6 +344,9 @@
     <x:t>61-9-2025-1152</x:t>
   </x:si>
   <x:si>
+    <x:t>1215898</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | October 2025</x:t>
   </x:si>
   <x:si>
@@ -317,6 +362,9 @@
     <x:t>61-10-2025-1185</x:t>
   </x:si>
   <x:si>
+    <x:t>1215952</x:t>
+  </x:si>
+  <x:si>
     <x:t>IAN CABANSAG GALLARDO</x:t>
   </x:si>
   <x:si>
@@ -329,6 +377,9 @@
     <x:t>61-10-2025-1194</x:t>
   </x:si>
   <x:si>
+    <x:t>1215958</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | November 2025</x:t>
   </x:si>
   <x:si>
@@ -344,6 +395,9 @@
     <x:t>61-10-2025-1192</x:t>
   </x:si>
   <x:si>
+    <x:t>1215998</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARLYN TENIR PASCO</x:t>
   </x:si>
   <x:si>
@@ -356,6 +410,9 @@
     <x:t>61-10-2025-1206</x:t>
   </x:si>
   <x:si>
+    <x:t>1215975</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUNITO MANGUBAT PONCE</x:t>
   </x:si>
   <x:si>
@@ -368,6 +425,9 @@
     <x:t>61-11-2025-1220</x:t>
   </x:si>
   <x:si>
+    <x:t>1215995</x:t>
+  </x:si>
+  <x:si>
     <x:t>FRANKLIN DURON SABIT</x:t>
   </x:si>
   <x:si>
@@ -380,6 +440,9 @@
     <x:t>61-11-2025-1227</x:t>
   </x:si>
   <x:si>
+    <x:t>1216011</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUEL BUGAS BALILI</x:t>
   </x:si>
   <x:si>
@@ -389,6 +452,9 @@
     <x:t>61-11-2025-1228</x:t>
   </x:si>
   <x:si>
+    <x:t>1216012</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | December 2025</x:t>
   </x:si>
   <x:si>
@@ -404,6 +470,9 @@
     <x:t>61-11-2025-1244-127</x:t>
   </x:si>
   <x:si>
+    <x:t>1216037</x:t>
+  </x:si>
+  <x:si>
     <x:t>GINA SUZON ALIVIO</x:t>
   </x:si>
   <x:si>
@@ -416,6 +485,9 @@
     <x:t>61-11-2025-1237</x:t>
   </x:si>
   <x:si>
+    <x:t>1216026</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | January 2026</x:t>
   </x:si>
   <x:si>
@@ -431,6 +503,9 @@
     <x:t>61-1-2026-1269-970</x:t>
   </x:si>
   <x:si>
+    <x:t>1216079</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDILBERTO ZUALSOLA TIGUELO</x:t>
   </x:si>
   <x:si>
@@ -443,6 +518,9 @@
     <x:t>61-1-2026-1268-653</x:t>
   </x:si>
   <x:si>
+    <x:t>1216071</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier 9</x:t>
   </x:si>
   <x:si>
@@ -452,6 +530,9 @@
     <x:t>61-1-2026-1267-387</x:t>
   </x:si>
   <x:si>
+    <x:t>1216072</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARDION QUIZO DOMINGUEZ</x:t>
   </x:si>
   <x:si>
@@ -464,6 +545,9 @@
     <x:t>61-1-2026-1277-866</x:t>
   </x:si>
   <x:si>
+    <x:t>1216095</x:t>
+  </x:si>
+  <x:si>
     <x:t>RAUL GALLEGO DIANAL</x:t>
   </x:si>
   <x:si>
@@ -476,6 +560,9 @@
     <x:t>61-1-2026-1273-054</x:t>
   </x:si>
   <x:si>
+    <x:t>1216082</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
@@ -494,6 +581,9 @@
     <x:t>61-2-2026-1341-726</x:t>
   </x:si>
   <x:si>
+    <x:t>1195996</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fortunata Postigo</x:t>
   </x:si>
   <x:si>
@@ -509,6 +599,9 @@
     <x:t>61-1-2026-1298-673</x:t>
   </x:si>
   <x:si>
+    <x:t>1216105</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUTIQUIO GERMINA BANAWAN</x:t>
   </x:si>
   <x:si>
@@ -521,6 +614,9 @@
     <x:t>61-2-2026-1309-810</x:t>
   </x:si>
   <x:si>
+    <x:t>1216128</x:t>
+  </x:si>
+  <x:si>
     <x:t>REYNALDO LUMBATAN ANITO</x:t>
   </x:si>
   <x:si>
@@ -533,6 +629,9 @@
     <x:t>61-2-2026-1323-800</x:t>
   </x:si>
   <x:si>
+    <x:t>1216135</x:t>
+  </x:si>
+  <x:si>
     <x:t>JOEL L. BAGUIO</x:t>
   </x:si>
   <x:si>
@@ -545,9 +644,27 @@
     <x:t>61-1-2026-1302-574</x:t>
   </x:si>
   <x:si>
+    <x:t>1216104</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
+    <x:t>ERMIE MAGHUYOP MAHINAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fisherville Purok fisherville, Lumbia, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IPHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1318-318</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216200</x:t>
+  </x:si>
+  <x:si>
     <x:t>FERNANDO B LAKAG</x:t>
   </x:si>
   <x:si>
@@ -560,6 +677,9 @@
     <x:t>61-2-2026-1322-666</x:t>
   </x:si>
   <x:si>
+    <x:t>1216139</x:t>
+  </x:si>
+  <x:si>
     <x:t>LILIA R. FLORIDA</x:t>
   </x:si>
   <x:si>
@@ -572,6 +692,9 @@
     <x:t>61-3-2026-1378-820</x:t>
   </x:si>
   <x:si>
+    <x:t>1216175</x:t>
+  </x:si>
+  <x:si>
     <x:t>MERIAM MANON-OG LICAYAN</x:t>
   </x:si>
   <x:si>
@@ -584,6 +707,9 @@
     <x:t>61-2-2026-1320-600</x:t>
   </x:si>
   <x:si>
+    <x:t>1216140</x:t>
+  </x:si>
+  <x:si>
     <x:t>MYRNA M MANUGAS</x:t>
   </x:si>
   <x:si>
@@ -596,6 +722,9 @@
     <x:t>61-3-2026-1381-306</x:t>
   </x:si>
   <x:si>
+    <x:t>1216177</x:t>
+  </x:si>
+  <x:si>
     <x:t>WILMA E BERMUDO</x:t>
   </x:si>
   <x:si>
@@ -608,6 +737,9 @@
     <x:t>61-3-2026-1379-115</x:t>
   </x:si>
   <x:si>
+    <x:t>1216176</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
   </x:si>
   <x:si>
@@ -620,6 +752,9 @@
     <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
+    <x:t>1216162</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARCHER C COTINA</x:t>
   </x:si>
   <x:si>
@@ -632,6 +767,9 @@
     <x:t>61-2-2026-1347-156</x:t>
   </x:si>
   <x:si>
+    <x:t>1216157</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHARLO F SALUMAG</x:t>
   </x:si>
   <x:si>
@@ -644,6 +782,9 @@
     <x:t>61-2-2026-1363-573</x:t>
   </x:si>
   <x:si>
+    <x:t>1216155</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLAUDIO E. ELNAR</x:t>
   </x:si>
   <x:si>
@@ -656,6 +797,9 @@
     <x:t>61-2-2026-1348-671</x:t>
   </x:si>
   <x:si>
+    <x:t>1216153</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDGAR S SERENCIO</x:t>
   </x:si>
   <x:si>
@@ -668,6 +812,9 @@
     <x:t>61-2-2026-1351-693</x:t>
   </x:si>
   <x:si>
+    <x:t>1216164</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN M SAGAYNO</x:t>
   </x:si>
   <x:si>
@@ -677,6 +824,9 @@
     <x:t>61-2-2026-1349-935</x:t>
   </x:si>
   <x:si>
+    <x:t>1216151</x:t>
+  </x:si>
+  <x:si>
     <x:t>PONCIANO O. SINDAY</x:t>
   </x:si>
   <x:si>
@@ -689,6 +839,9 @@
     <x:t>61-2-2026-1365-581</x:t>
   </x:si>
   <x:si>
+    <x:t>1216159</x:t>
+  </x:si>
+  <x:si>
     <x:t>RAMON M SILVA</x:t>
   </x:si>
   <x:si>
@@ -698,6 +851,9 @@
     <x:t>61-2-2026-1350-437</x:t>
   </x:si>
   <x:si>
+    <x:t>1216149</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROBERTO Q CORPIN</x:t>
   </x:si>
   <x:si>
@@ -710,6 +866,9 @@
     <x:t>61-2-2026-1361-291</x:t>
   </x:si>
   <x:si>
+    <x:t>1216166</x:t>
+  </x:si>
+  <x:si>
     <x:t>RODEL PALMERO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -722,6 +881,9 @@
     <x:t>61-2-2026-1336-018</x:t>
   </x:si>
   <x:si>
+    <x:t>1216191</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROMEO CAPANGPANGAN DUMAOG</x:t>
   </x:si>
   <x:si>
@@ -732,6 +894,9 @@
   </x:si>
   <x:si>
     <x:t>61-3-2026-1390-540</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216192</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1580,7 +1745,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>171</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -1655,269 +1820,269 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46065.33125</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="29" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>46062.3800913889</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="33">
+        <x:v>46104.0851025694</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="29" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46065.3312544444</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45700</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216139</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46084.1560763889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46085.2764814815</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216175</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46093.2000115741</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>46084.1560858449</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>181</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46065.2288541667</x:v>
+        <x:v>46085.2764846181</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216140</x:v>
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="s">
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
-        <x:v>390</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46084.1582175926</x:v>
+        <x:v>46093.2000157407</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46085.3007986111</x:v>
+        <x:v>46065.2288648495</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46386</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216177</x:v>
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="s">
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
-        <x:v>300</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46093.215162037</x:v>
+        <x:v>46084.1582202315</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46085.2858333333</x:v>
+        <x:v>46085.3008007755</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46096</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1216176</x:v>
+        <x:v>46386</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="s">
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
-        <x:v>390</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46093.2057060185</x:v>
+        <x:v>46093.2151637732</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>193</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46072.3153009259</x:v>
+        <x:v>46085.2858432523</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1216162</x:v>
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="s">
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46090.311412037</x:v>
+        <x:v>46093.2057128819</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>199</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46072.3153026736</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="n">
-        <x:v>1216157</x:v>
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="s">
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.3114235417</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -1925,37 +2090,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G15" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46073.0262962616</x:v>
       </x:c>
       <x:c r="I15" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J15" s="30" t="n">
-        <x:v>1216155</x:v>
+      <x:c r="J15" s="30" t="s">
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.2670310069</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -1963,37 +2128,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="29" t="s">
-        <x:v>204</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D16" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="F16" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G16" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46077.2103691435</x:v>
       </x:c>
       <x:c r="I16" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J16" s="30" t="n">
-        <x:v>1216153</x:v>
+      <x:c r="J16" s="30" t="s">
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.253629537</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -2001,37 +2166,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="D17" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E17" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="F17" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G17" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0478536458</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J17" s="30" t="n">
-        <x:v>1216164</x:v>
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J17" s="30" t="s">
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.2431909954</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -2039,37 +2204,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D18" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G18" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.10951125</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="n">
-        <x:v>1216151</x:v>
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="s">
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46091.1210900116</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -2077,37 +2242,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C19" s="29" t="s">
-        <x:v>215</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D19" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="29" t="s">
-        <x:v>216</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G19" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.0611031366</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J19" s="30" t="n">
-        <x:v>1216159</x:v>
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J19" s="30" t="s">
+        <x:v>264</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2266513079</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -2115,37 +2280,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D20" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E20" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G20" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683575231</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J20" s="30" t="n">
-        <x:v>1216149</x:v>
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="s">
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806125347</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -2153,37 +2318,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D21" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G21" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46073.0763545833</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J21" s="30" t="n">
-        <x:v>1216166</x:v>
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J21" s="30" t="s">
+        <x:v>273</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2162962268</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -2191,37 +2356,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>229</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46071.2853587963</x:v>
+        <x:v>46077.1834319213</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J22" s="30" t="n">
-        <x:v>1216191</x:v>
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J22" s="30" t="s">
+        <x:v>278</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46094.1777199074</x:v>
+        <x:v>46091.2388780324</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -2229,106 +2394,143 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D23" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E23" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>232</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46090.3681365741</x:v>
+        <x:v>46071.2853697569</x:v>
       </x:c>
       <x:c r="I23" s="31">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="K23" s="32" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L23" s="33">
+        <x:v>46094.1777229282</x:v>
+      </x:c>
+      <x:c r="M23" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D24" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="29" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F24" s="29" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G24" s="29" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H24" s="31">
+        <x:v>46090.3681394907</x:v>
+      </x:c>
+      <x:c r="I24" s="31">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J23" s="30" t="n">
-        <x:v>1216192</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
+      <x:c r="J24" s="30" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L23" s="33">
-        <x:v>46094.182662037</x:v>
-      </x:c>
-      <x:c r="M23" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="L24" s="33">
+        <x:v>46094.1826630093</x:v>
+      </x:c>
+      <x:c r="M24" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C26" s="18" t="s"/>
-      <x:c r="D26" s="18" t="s"/>
-      <x:c r="E26" s="19" t="s"/>
-      <x:c r="F26" s="19" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="20" t="s">
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C27" s="21" t="s"/>
-      <x:c r="D27" s="21" t="s"/>
-      <x:c r="E27" s="21" t="s"/>
-      <x:c r="F27" s="22" t="s">
+      <x:c r="C27" s="18" t="s"/>
+      <x:c r="D27" s="18" t="s"/>
+      <x:c r="E27" s="19" t="s"/>
+      <x:c r="F27" s="19" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C28" s="24" t="s"/>
-      <x:c r="D28" s="24" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="25" t="n">
-        <x:v>5</x:v>
+      <x:c r="C28" s="21" t="s"/>
+      <x:c r="D28" s="21" t="s"/>
+      <x:c r="E28" s="21" t="s"/>
+      <x:c r="F28" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="23" t="s">
-        <x:v>52</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="24" t="s"/>
       <x:c r="D29" s="24" t="s"/>
       <x:c r="E29" s="24" t="s"/>
       <x:c r="F29" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="23" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C30" s="24" t="s"/>
       <x:c r="D30" s="24" t="s"/>
       <x:c r="E30" s="24" t="s"/>
       <x:c r="F30" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C31" s="24" t="s"/>
+      <x:c r="D31" s="24" t="s"/>
+      <x:c r="E31" s="24" t="s"/>
+      <x:c r="F31" s="25" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3296,12 +3498,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B26:F26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3507,22 +3709,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>45861.181087963</x:v>
+        <x:v>45861.1810907407</x:v>
       </x:c>
       <x:c r="I8" s="15">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215835</x:v>
+      <x:c r="J8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>330</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>45862.1344560185</x:v>
+        <x:v>45862.1344605671</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3542,7 +3744,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -3551,13 +3753,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
@@ -3573,7 +3775,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>
@@ -4682,7 +4884,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4757,269 +4959,269 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="C8" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45881.1074421296</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="G8" s="29" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>45881.1074470139</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
         <x:v>45889</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1195698</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45882.1141782407</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>32</x:v>
+      <x:c r="L8" s="33">
+        <x:v>45882.1141826157</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="F9" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>45881.2688653125</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>37</x:v>
+      <x:c r="L9" s="33">
+        <x:v>45882.0237933565</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>45897.2409837963</x:v>
+        <x:v>45897.2409947801</x:v>
       </x:c>
       <x:c r="I10" s="31">
         <x:v>45681</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1346493</x:v>
+      <x:c r="J10" s="30" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>45897.2777430556</x:v>
+        <x:v>45897.2777466898</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>45875.2668402778</x:v>
+        <x:v>45875.2668430556</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>45875.2668518519</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1215854</x:v>
+        <x:v>45875.2668525</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>45877.2327314815</x:v>
+        <x:v>45877.2327351852</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>45889.2616782407</x:v>
+        <x:v>45889.2616895949</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1215867</x:v>
+        <x:v>45889.2616989468</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="s">
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>45891.1582986111</x:v>
+        <x:v>45891.1583043171</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>45889.1521064815</x:v>
+        <x:v>45889.1521108681</x:v>
       </x:c>
       <x:c r="I13" s="31">
         <x:v>44272</x:v>
       </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1215866</x:v>
+      <x:c r="J13" s="30" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
         <x:v>600</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>45891.153287037</x:v>
+        <x:v>45891.1532978241</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="29" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>45887.5499305556</x:v>
+        <x:v>45887.5499379745</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>45887.5499537037</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="n">
-        <x:v>1215865</x:v>
+        <x:v>45887.5499545023</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="s">
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>45891.1027199074</x:v>
+        <x:v>45891.1027280787</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -5027,44 +5229,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G15" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>45883.2595717593</x:v>
+        <x:v>45883.2595720718</x:v>
       </x:c>
       <x:c r="I15" s="31">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J15" s="30" t="n">
-        <x:v>1346470</x:v>
+      <x:c r="J15" s="30" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>480</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>45883.2880208333</x:v>
+        <x:v>45883.2880279051</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="18" t="s"/>
       <x:c r="D18" s="18" t="s"/>
@@ -5073,18 +5275,18 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
       <x:c r="B19" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="21" t="s"/>
       <x:c r="D19" s="21" t="s"/>
       <x:c r="E19" s="21" t="s"/>
       <x:c r="F19" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="24" t="s"/>
       <x:c r="D20" s="24" t="s"/>
@@ -5095,7 +5297,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="23" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="24" t="s"/>
       <x:c r="D21" s="24" t="s"/>
@@ -5106,7 +5308,7 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="23" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C22" s="24" t="s"/>
       <x:c r="D22" s="24" t="s"/>
@@ -5117,7 +5319,7 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="23" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="24" t="s"/>
       <x:c r="D23" s="24" t="s"/>
@@ -5139,7 +5341,7 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
       <x:c r="B25" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C25" s="27" t="s"/>
       <x:c r="D25" s="27" t="s"/>
@@ -6241,7 +6443,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6316,117 +6518,117 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45902.1777546296</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="29" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>45902.1777587269</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
         <x:v>45781</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215887</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45911.9486574074</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>45911.9486641782</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="E9" s="29" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>45887.291765787</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>45903.117765081</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>75</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>45911.4396296296</x:v>
+        <x:v>45911.4396314699</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1215899</x:v>
+        <x:v>45911.4396406018</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>45918.0952083333</x:v>
+        <x:v>45918.0952106019</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -6434,37 +6636,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>78</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>79</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>45925.3972453704</x:v>
+        <x:v>45925.397251713</x:v>
       </x:c>
       <x:c r="I11" s="31">
         <x:v>47021</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1215915</x:v>
+      <x:c r="J11" s="30" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>45930.1169560185</x:v>
+        <x:v>45930.1169604282</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -6472,37 +6674,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>45916.1769097222</x:v>
+        <x:v>45916.1769203588</x:v>
       </x:c>
       <x:c r="I12" s="31">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1215916</x:v>
+      <x:c r="J12" s="30" t="s">
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>45930.1671643518</x:v>
+        <x:v>45930.1671706366</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -6510,44 +6712,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>89</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>45912.47375</x:v>
+        <x:v>45912.4737565972</x:v>
       </x:c>
       <x:c r="I13" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1215898</x:v>
+      <x:c r="J13" s="30" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>45918.0905787037</x:v>
+        <x:v>45918.0905875926</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="18" t="s"/>
       <x:c r="D16" s="18" t="s"/>
@@ -6556,18 +6758,18 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
       <x:c r="B17" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="21" t="s"/>
       <x:c r="D17" s="21" t="s"/>
       <x:c r="E17" s="21" t="s"/>
       <x:c r="F17" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="24" t="s"/>
       <x:c r="D18" s="24" t="s"/>
@@ -6578,7 +6780,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="23" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C19" s="24" t="s"/>
       <x:c r="D19" s="24" t="s"/>
@@ -6600,7 +6802,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
@@ -7704,7 +7906,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -7779,86 +7981,86 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45938.0053703704</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="29" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>45938.0053813889</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215952</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="30" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45945.1196180556</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>45945.1196250694</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="C9" s="29" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45945.2727662037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="E9" s="29" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>45945.2727709838</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215958</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45953.151099537</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>45953.1511070255</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="18" t="s"/>
       <x:c r="D12" s="18" t="s"/>
@@ -7867,18 +8069,18 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
       <x:c r="B13" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="21" t="s"/>
       <x:c r="D13" s="21" t="s"/>
       <x:c r="E13" s="21" t="s"/>
       <x:c r="F13" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
       <x:c r="B14" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="24" t="s"/>
       <x:c r="D14" s="24" t="s"/>
@@ -7900,7 +8102,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
@@ -9008,7 +9210,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -9083,117 +9285,117 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>45944.1129354167</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="30" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>45971.3164108796</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45954.1265625</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="E9" s="29" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>45954.1265640162</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45626</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215975</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45967.0018287037</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>45967.0018301736</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>109</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>45965.2541435185</x:v>
+        <x:v>45965.2541525</x:v>
       </x:c>
       <x:c r="I10" s="31">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1215995</x:v>
+      <x:c r="J10" s="30" t="s">
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>45971.1502199074</x:v>
+        <x:v>45971.1502294097</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -9201,37 +9403,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>112</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>45966.1203125</x:v>
+        <x:v>45966.1203235417</x:v>
       </x:c>
       <x:c r="I11" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216011</x:v>
+      <x:c r="J11" s="30" t="s">
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>45975.3046180556</x:v>
+        <x:v>45975.3046220602</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -9239,44 +9441,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>45966.1218055556</x:v>
+        <x:v>45966.1218093634</x:v>
       </x:c>
       <x:c r="I12" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1216012</x:v>
+      <x:c r="J12" s="30" t="s">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>45975.312349537</x:v>
+        <x:v>45975.3123537269</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="18" t="s"/>
       <x:c r="D15" s="18" t="s"/>
@@ -9285,18 +9487,18 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
       <x:c r="B16" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="21" t="s"/>
       <x:c r="D16" s="21" t="s"/>
       <x:c r="E16" s="21" t="s"/>
       <x:c r="F16" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="24" t="s"/>
       <x:c r="D17" s="24" t="s"/>
@@ -9318,7 +9520,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
@@ -10423,7 +10625,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -10498,86 +10700,86 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="C8" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45979.0549768519</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="29" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>45979.0549779514</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46006.2690046296</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>46006.269013287</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="C9" s="29" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45972.2314236111</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="E9" s="29" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>45972.2314280556</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216026</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45992.0065509259</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>45992.0065612963</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="18" t="s"/>
       <x:c r="D12" s="18" t="s"/>
@@ -10586,13 +10788,13 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
       <x:c r="B13" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="21" t="s"/>
       <x:c r="D13" s="21" t="s"/>
       <x:c r="E13" s="21" t="s"/>
       <x:c r="F13" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
@@ -10608,7 +10810,7 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
       <x:c r="B15" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="27" t="s"/>
       <x:c r="D15" s="27" t="s"/>
@@ -11716,7 +11918,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -11791,79 +11993,79 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="29" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>46031.0429770602</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
         <x:v>46015</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="30" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>46043.2977226505</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="E9" s="29" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46029.1168153009</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46036.0526736111</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>137</x:v>
+      <x:c r="L9" s="33">
+        <x:v>46036.0526802894</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -11871,37 +12073,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>138</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46029.112962963</x:v>
+        <x:v>46029.1129715509</x:v>
       </x:c>
       <x:c r="I10" s="31">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216072</x:v>
+      <x:c r="J10" s="30" t="s">
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46036.0583564815</x:v>
+        <x:v>46036.0583638426</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -11909,37 +12111,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>141</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46036.929224537</x:v>
+        <x:v>46036.9292262963</x:v>
       </x:c>
       <x:c r="I11" s="31">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216095</x:v>
+      <x:c r="J11" s="30" t="s">
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46050.0472337963</x:v>
+        <x:v>46050.0472434028</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -11947,44 +12149,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>144</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>147</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46034.1741087963</x:v>
+        <x:v>46034.174115162</x:v>
       </x:c>
       <x:c r="I12" s="31">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1216082</x:v>
+      <x:c r="J12" s="30" t="s">
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46044.2691666667</x:v>
+        <x:v>46044.2691750116</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="18" t="s"/>
       <x:c r="D15" s="18" t="s"/>
@@ -11993,18 +12195,18 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
       <x:c r="B16" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="21" t="s"/>
       <x:c r="D16" s="21" t="s"/>
       <x:c r="E16" s="21" t="s"/>
       <x:c r="F16" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="24" t="s"/>
       <x:c r="D17" s="24" t="s"/>
@@ -12015,7 +12217,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="23" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="24" t="s"/>
       <x:c r="D18" s="24" t="s"/>
@@ -12037,7 +12239,7 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
@@ -13142,7 +13344,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -13217,155 +13419,155 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46072.0406597222</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46077.0821759259</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1195996</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="B8" s="29" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E8" s="29" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>46072.0406637037</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46077.082186713</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46078.028275463</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>154</x:v>
+      <x:c r="L8" s="33">
+        <x:v>46078.028276956</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="E9" s="29" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46050.1475945255</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
         <x:v>45988</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>46057.9737815278</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>160</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>161</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46057.234375</x:v>
+        <x:v>46057.2343839583</x:v>
       </x:c>
       <x:c r="I10" s="31">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216128</x:v>
+      <x:c r="J10" s="30" t="s">
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>630</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46072.0668055556</x:v>
+        <x:v>46072.0668155208</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="29" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>163</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46066.1502662037</x:v>
+        <x:v>46066.1502727199</x:v>
       </x:c>
       <x:c r="I11" s="31">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216135</x:v>
+      <x:c r="J11" s="30" t="s">
+        <x:v>199</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46077.9542708333</x:v>
+        <x:v>46077.954281088</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -13373,44 +13575,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46051.2882638889</x:v>
+        <x:v>46051.2882746759</x:v>
       </x:c>
       <x:c r="I12" s="31">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1216104</x:v>
+      <x:c r="J12" s="30" t="s">
+        <x:v>204</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>960</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46057.963587963</x:v>
+        <x:v>46057.9635980093</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="18" t="s"/>
       <x:c r="D15" s="18" t="s"/>
@@ -13419,18 +13621,18 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
       <x:c r="B16" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="21" t="s"/>
       <x:c r="D16" s="21" t="s"/>
       <x:c r="E16" s="21" t="s"/>
       <x:c r="F16" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="23" t="s">
-        <x:v>149</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C17" s="24" t="s"/>
       <x:c r="D17" s="24" t="s"/>
@@ -13441,7 +13643,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="24" t="s"/>
       <x:c r="D18" s="24" t="s"/>
@@ -13463,7 +13665,7 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1778,7 +1778,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1818,7 +1818,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -1857,7 +1857,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -1895,7 +1895,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -1933,7 +1933,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -1971,7 +1971,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -2009,7 +2009,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -2047,7 +2047,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
@@ -2085,7 +2085,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2123,7 +2123,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2161,7 +2161,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2199,7 +2199,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2237,7 +2237,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2275,7 +2275,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2313,7 +2313,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2351,7 +2351,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2389,7 +2389,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2427,7 +2427,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3648,7 +3648,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3688,7 +3688,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -4917,7 +4917,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4957,7 +4957,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -4996,7 +4996,7 @@
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -5034,7 +5034,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -5072,7 +5072,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>46</x:v>
       </x:c>
@@ -5110,7 +5110,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>46</x:v>
       </x:c>
@@ -5148,7 +5148,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
@@ -5186,7 +5186,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
@@ -5224,7 +5224,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6476,7 +6476,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -6516,7 +6516,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -6555,7 +6555,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -6593,7 +6593,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
@@ -6631,7 +6631,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6669,7 +6669,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6707,7 +6707,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7939,7 +7939,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -7979,7 +7979,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -8018,7 +8018,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9243,7 +9243,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -9283,7 +9283,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -9322,7 +9322,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -9360,7 +9360,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -9398,7 +9398,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9436,7 +9436,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -10658,7 +10658,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -10698,7 +10698,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>15</x:v>
@@ -10737,7 +10737,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11951,7 +11951,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -11991,7 +11991,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -12030,7 +12030,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
@@ -12068,7 +12068,7 @@
         <x:v>163</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12106,7 +12106,7 @@
         <x:v>163</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12144,7 +12144,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -13377,7 +13377,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -13417,7 +13417,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>178</x:v>
@@ -13456,7 +13456,7 @@
         <x:v>184</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -13494,7 +13494,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -13532,7 +13532,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -13570,7 +13570,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="280">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -38,9 +38,6 @@
     <x:t>CERTIFICATES SUMMARY</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | July 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -113,9 +110,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | August 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -254,9 +248,6 @@
     <x:t>1346470</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | September 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>ARNEL REPOSAR CANDANO</x:t>
   </x:si>
   <x:si>
@@ -347,9 +338,6 @@
     <x:t>1215898</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | October 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>EDWIN ALMENDRAL ALCORIZA</x:t>
   </x:si>
   <x:si>
@@ -380,9 +368,6 @@
     <x:t>1215958</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | November 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>AGAPITO PERATER BERALLO</x:t>
   </x:si>
   <x:si>
@@ -455,9 +440,6 @@
     <x:t>1216012</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | December 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>CRESENCIO CUA JUSAY</x:t>
   </x:si>
   <x:si>
@@ -488,9 +470,6 @@
     <x:t>1216026</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | January 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARENIE CAJETAS FLORA</x:t>
   </x:si>
   <x:si>
@@ -563,9 +542,6 @@
     <x:t>1216082</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
@@ -645,9 +621,6 @@
   </x:si>
   <x:si>
     <x:t>1216104</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>ERMIE MAGHUYOP MAHINAY</x:t>
@@ -1235,7 +1208,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1250,6 +1223,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1322,7 +1298,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1358,6 +1334,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1744,20 +1724,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1780,754 +1760,754 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>46062.3800913889</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46104.0851025694</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
+        <x:v>46065.3312544444</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45700</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="K9" s="33" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46084.1560858449</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="F10" s="30" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>46062.3800913889</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+      <x:c r="G10" s="30" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L8" s="33">
-        <x:v>46104.0851025694</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="H10" s="32">
+        <x:v>46085.2764846181</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
+      <x:c r="K10" s="33" t="n">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>46093.2000157407</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G9" s="29" t="s">
+      <x:c r="F11" s="30" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="H9" s="31">
-        <x:v>46065.3312544444</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45700</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L9" s="33">
-        <x:v>46084.1560858449</x:v>
-      </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="H11" s="32">
+        <x:v>46065.2288648495</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
+      <x:c r="K11" s="33" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>46084.1582202315</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="F10" s="29" t="s">
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="F12" s="30" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>46085.2764846181</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
+      <x:c r="G12" s="30" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46093.2000157407</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46085.3008007755</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46386</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
+      <x:c r="K12" s="33" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L12" s="34">
+        <x:v>46093.2151637732</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="s">
+      <x:c r="D13" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G11" s="29" t="s">
+      <x:c r="F13" s="30" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H11" s="31">
-        <x:v>46065.2288648495</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
+      <x:c r="G13" s="30" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="H13" s="32">
+        <x:v>46085.2858432523</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K13" s="33" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46084.1582202315</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
+      <x:c r="L13" s="34">
+        <x:v>46093.2057128819</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="s">
+      <x:c r="D14" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="G12" s="29" t="s">
+      <x:c r="F14" s="30" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="H12" s="31">
-        <x:v>46085.3008007755</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>46386</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
+      <x:c r="G14" s="30" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>46093.2151637732</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
+      <x:c r="H14" s="32">
+        <x:v>46072.3153026736</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
+      <x:c r="K14" s="33" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L14" s="34">
+        <x:v>46090.3114235417</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="F13" s="29" t="s">
+      <x:c r="D15" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G13" s="29" t="s">
+      <x:c r="F15" s="30" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="H13" s="31">
-        <x:v>46085.2858432523</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>46096</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="s">
+      <x:c r="G15" s="30" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>46093.2057128819</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46073.0262962616</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="D14" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="s">
+      <x:c r="K15" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L15" s="34">
+        <x:v>46090.2670310069</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F14" s="29" t="s">
+      <x:c r="D16" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G14" s="29" t="s">
+      <x:c r="F16" s="30" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H14" s="31">
-        <x:v>46072.3153026736</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="s">
+      <x:c r="G16" s="30" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="K14" s="32" t="n">
+      <x:c r="H16" s="32">
+        <x:v>46077.2103691435</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="K16" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L16" s="34">
+        <x:v>46090.253629537</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46073.0478536458</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="K17" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L17" s="34">
+        <x:v>46090.2431909954</x:v>
+      </x:c>
+      <x:c r="M17" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46073.10951125</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="K18" s="33" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L14" s="33">
-        <x:v>46090.3114235417</x:v>
-      </x:c>
-      <x:c r="M14" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D15" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="29" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F15" s="29" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G15" s="29" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H15" s="31">
-        <x:v>46073.0262962616</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J15" s="30" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
+      <x:c r="L18" s="34">
+        <x:v>46091.1210900116</x:v>
+      </x:c>
+      <x:c r="M18" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46073.0611031366</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="K19" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L15" s="33">
-        <x:v>46090.2670310069</x:v>
-      </x:c>
-      <x:c r="M15" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D16" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="29" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F16" s="29" t="s">
+      <x:c r="L19" s="34">
+        <x:v>46090.2266513079</x:v>
+      </x:c>
+      <x:c r="M19" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46077.2683575231</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K20" s="33" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="34">
+        <x:v>46090.2806125347</x:v>
+      </x:c>
+      <x:c r="M20" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="G16" s="29" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H16" s="31">
-        <x:v>46077.2103691435</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J16" s="30" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L16" s="33">
-        <x:v>46090.253629537</x:v>
-      </x:c>
-      <x:c r="M16" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="D17" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="29" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F17" s="29" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G17" s="29" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H17" s="31">
-        <x:v>46073.0478536458</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J17" s="30" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L17" s="33">
-        <x:v>46090.2431909954</x:v>
-      </x:c>
-      <x:c r="M17" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D18" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="29" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F18" s="29" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G18" s="29" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46073.10951125</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
+      <x:c r="F21" s="30" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46073.0763545833</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J18" s="30" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
+      <x:c r="J21" s="31" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="K21" s="33" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L18" s="33">
-        <x:v>46091.1210900116</x:v>
-      </x:c>
-      <x:c r="M18" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="D19" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="29" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F19" s="29" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="G19" s="29" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H19" s="31">
-        <x:v>46073.0611031366</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J19" s="30" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L19" s="33">
-        <x:v>46090.2266513079</x:v>
-      </x:c>
-      <x:c r="M19" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s">
+      <x:c r="L21" s="34">
+        <x:v>46090.2162962268</x:v>
+      </x:c>
+      <x:c r="M21" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="D20" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="29" t="s">
+      <x:c r="D22" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="F20" s="29" t="s">
+      <x:c r="F22" s="30" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="s">
+      <x:c r="G22" s="30" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="H20" s="31">
-        <x:v>46077.2683575231</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
+      <x:c r="H22" s="32">
+        <x:v>46077.1834319213</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="K22" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L22" s="34">
+        <x:v>46091.2388780324</x:v>
+      </x:c>
+      <x:c r="M22" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46071.2853697569</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J20" s="30" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
+      <x:c r="J23" s="31" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="K23" s="33" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L20" s="33">
-        <x:v>46090.2806125347</x:v>
-      </x:c>
-      <x:c r="M20" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D21" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="29" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F21" s="29" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="G21" s="29" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H21" s="31">
-        <x:v>46073.0763545833</x:v>
-      </x:c>
-      <x:c r="I21" s="31">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J21" s="30" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L21" s="33">
-        <x:v>46090.2162962268</x:v>
-      </x:c>
-      <x:c r="M21" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D22" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="29" t="s">
+      <x:c r="L23" s="34">
+        <x:v>46094.1777229282</x:v>
+      </x:c>
+      <x:c r="M23" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="F22" s="29" t="s">
+      <x:c r="D24" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="G22" s="29" t="s">
+      <x:c r="F24" s="30" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="H22" s="31">
-        <x:v>46077.1834319213</x:v>
-      </x:c>
-      <x:c r="I22" s="31">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J22" s="30" t="s">
+      <x:c r="G24" s="30" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="K22" s="32" t="n">
+      <x:c r="H24" s="32">
+        <x:v>46090.3681394907</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L22" s="33">
-        <x:v>46091.2388780324</x:v>
-      </x:c>
-      <x:c r="M22" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="D23" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E23" s="29" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="F23" s="29" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G23" s="29" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H23" s="31">
-        <x:v>46071.2853697569</x:v>
-      </x:c>
-      <x:c r="I23" s="31">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J23" s="30" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L23" s="33">
-        <x:v>46094.1777229282</x:v>
-      </x:c>
-      <x:c r="M23" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D24" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="29" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F24" s="29" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G24" s="29" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H24" s="31">
-        <x:v>46090.3681394907</x:v>
-      </x:c>
-      <x:c r="I24" s="31">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J24" s="30" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L24" s="33">
+      <x:c r="L24" s="34">
         <x:v>46094.1826630093</x:v>
       </x:c>
-      <x:c r="M24" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M24" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="17" t="s">
+      <x:c r="B27" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C27" s="19" t="s"/>
+      <x:c r="D27" s="19" t="s"/>
+      <x:c r="E27" s="20" t="s"/>
+      <x:c r="F27" s="20" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C27" s="18" t="s"/>
-      <x:c r="D27" s="18" t="s"/>
-      <x:c r="E27" s="19" t="s"/>
-      <x:c r="F27" s="19" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="20" t="s">
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="21" t="s"/>
-      <x:c r="F28" s="22" t="s">
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="24" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C29" s="24" t="s"/>
-      <x:c r="D29" s="24" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C30" s="24" t="s"/>
-      <x:c r="D30" s="24" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C31" s="24" t="s"/>
-      <x:c r="D31" s="24" t="s"/>
-      <x:c r="E31" s="24" t="s"/>
-      <x:c r="F31" s="25" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3614,20 +3594,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3650,81 +3630,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>45861.1810907407</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45861.1810907407</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>45862.1344605671</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45862.1344605671</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3743,44 +3723,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4883,20 +4863,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4919,434 +4899,434 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="F8" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="H8" s="32">
+        <x:v>45881.1074470139</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45889</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="K8" s="33" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45882.1141826157</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>45881.1074470139</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>45889</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
+        <x:v>45881.2688653125</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="33">
-        <x:v>45882.1141826157</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
+      <x:c r="L9" s="34">
+        <x:v>45882.0237933565</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H9" s="31">
-        <x:v>45881.2688653125</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K9" s="32" t="n">
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45897.2409947801</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="33">
-        <x:v>45882.0237933565</x:v>
-      </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="L10" s="34">
+        <x:v>45897.2777466898</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45897.2409947801</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
+      <x:c r="C11" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45897.2777466898</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="E11" s="30" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
+      <x:c r="F11" s="30" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E11" s="29" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="s">
+      <x:c r="H11" s="32">
+        <x:v>45875.2668430556</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>45875.2668525</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G11" s="29" t="s">
+      <x:c r="K11" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>45877.2327351852</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45875.2668430556</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45875.2668525</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
+      <x:c r="D12" s="31" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="F12" s="30" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45889.2616895949</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>45889.2616989468</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K12" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45877.2327351852</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
+      <x:c r="L12" s="34">
+        <x:v>45891.1583043171</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>45889.1521108681</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>44272</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K13" s="33" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L13" s="34">
+        <x:v>45891.1532978241</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>45889.2616895949</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45889.2616989468</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45891.1583043171</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>45889.1521108681</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>44272</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45891.1532978241</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+      <x:c r="E14" s="30" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C14" s="29" t="s">
+      <x:c r="F14" s="30" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D14" s="30" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="s">
+      <x:c r="G14" s="30" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F14" s="29" t="s">
+      <x:c r="H14" s="32">
+        <x:v>45887.5499379745</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>45887.5499545023</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G14" s="29" t="s">
+      <x:c r="K14" s="33" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L14" s="34">
+        <x:v>45891.1027280787</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H14" s="31">
-        <x:v>45887.5499379745</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>45887.5499545023</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="s">
+      <x:c r="D15" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L14" s="33">
-        <x:v>45891.1027280787</x:v>
-      </x:c>
-      <x:c r="M14" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s">
+      <x:c r="F15" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D15" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="29" t="s">
+      <x:c r="G15" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F15" s="29" t="s">
+      <x:c r="H15" s="32">
+        <x:v>45883.2595720718</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G15" s="29" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H15" s="31">
-        <x:v>45883.2595720718</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J15" s="30" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
+      <x:c r="K15" s="33" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="33">
+      <x:c r="L15" s="34">
         <x:v>45883.2880279051</x:v>
       </x:c>
-      <x:c r="M15" s="29" t="s">
-        <x:v>40</x:v>
+      <x:c r="M15" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="17" t="s">
+      <x:c r="B18" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C18" s="19" t="s"/>
+      <x:c r="D18" s="19" t="s"/>
+      <x:c r="E18" s="20" t="s"/>
+      <x:c r="F18" s="20" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C18" s="18" t="s"/>
-      <x:c r="D18" s="18" t="s"/>
-      <x:c r="E18" s="19" t="s"/>
-      <x:c r="F18" s="19" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="21" t="s"/>
-      <x:c r="F19" s="22" t="s">
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="24" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="24" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="24" t="s"/>
-      <x:c r="F22" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C23" s="24" t="s"/>
-      <x:c r="D23" s="24" t="s"/>
-      <x:c r="E23" s="24" t="s"/>
-      <x:c r="F23" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C24" s="24" t="s"/>
-      <x:c r="D24" s="24" t="s"/>
-      <x:c r="E24" s="24" t="s"/>
-      <x:c r="F24" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6442,20 +6422,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45901</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6478,336 +6458,336 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="H8" s="32">
+        <x:v>45902.1777587269</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45781</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="K8" s="33" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45911.9486641782</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>45902.1777587269</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>45781</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="G9" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
+        <x:v>45887.291765787</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="33">
-        <x:v>45911.9486641782</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
+      <x:c r="L9" s="34">
+        <x:v>45903.117765081</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G9" s="29" t="s">
+      <x:c r="D10" s="31" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H9" s="31">
-        <x:v>45887.291765787</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
+      <x:c r="F10" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L9" s="33">
-        <x:v>45903.117765081</x:v>
-      </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="G10" s="30" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
+      <x:c r="H10" s="32">
+        <x:v>45911.4396314699</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>45911.4396406018</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F10" s="29" t="s">
+      <x:c r="K10" s="33" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>45918.0952106019</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45911.4396314699</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45911.4396406018</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
+      <x:c r="F11" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45918.0952106019</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
+      <x:c r="H11" s="32">
+        <x:v>45925.397251713</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>47021</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="s">
+      <x:c r="K11" s="33" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>45930.1169604282</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G11" s="29" t="s">
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45925.397251713</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>47021</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
+      <x:c r="F12" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45930.1169604282</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
+      <x:c r="G12" s="30" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
+      <x:c r="H12" s="32">
+        <x:v>45916.1769203588</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="s">
+      <x:c r="K12" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="34">
+        <x:v>45930.1671706366</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G12" s="29" t="s">
+      <x:c r="D13" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="H12" s="31">
-        <x:v>45916.1769203588</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
+      <x:c r="F13" s="30" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45930.1671706366</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
+      <x:c r="G13" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
+      <x:c r="H13" s="32">
+        <x:v>45912.4737565972</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>45912.4737565972</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
+      <x:c r="K13" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="33">
+      <x:c r="L13" s="34">
         <x:v>45918.0905875926</x:v>
       </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="17" t="s">
+      <x:c r="B16" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="20" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C16" s="18" t="s"/>
-      <x:c r="D16" s="18" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="19" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="20" t="s">
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="21" t="s"/>
-      <x:c r="F17" s="22" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="24" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7905,20 +7885,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45931</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7941,173 +7921,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>45938.0053813889</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="K8" s="33" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45945.1196250694</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>45938.0053813889</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L8" s="33">
-        <x:v>45945.1196250694</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="H9" s="32">
+        <x:v>45945.2727709838</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45911</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
-        <x:v>45945.2727709838</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45911</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
+      <x:c r="K9" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="33">
+      <x:c r="L9" s="34">
         <x:v>45953.1511070255</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -9209,20 +9189,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45962</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9245,287 +9225,287 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>45944.1129354167</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45971.3164108796</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>45944.1129354167</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+      <x:c r="H9" s="32">
+        <x:v>45954.1265640162</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45626</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L8" s="33">
-        <x:v>45971.3164108796</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="K9" s="33" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>45967.0018301736</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="s">
+      <x:c r="F10" s="30" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G9" s="29" t="s">
+      <x:c r="G10" s="30" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H9" s="31">
-        <x:v>45954.1265640162</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45626</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
+      <x:c r="H10" s="32">
+        <x:v>45965.2541525</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>45971</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L9" s="33">
-        <x:v>45967.0018301736</x:v>
-      </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="K10" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>45971.1502294097</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F10" s="29" t="s">
+      <x:c r="F11" s="30" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45965.2541525</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45971</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
+      <x:c r="H11" s="32">
+        <x:v>45966.1203235417</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45971.1502294097</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="L11" s="34">
+        <x:v>45975.3046220602</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="s">
+      <x:c r="G12" s="30" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G11" s="29" t="s">
+      <x:c r="H12" s="32">
+        <x:v>45966.1218093634</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45966.1203235417</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45975.3046220602</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>45966.1218093634</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
+      <x:c r="L12" s="34">
         <x:v>45975.3123537269</x:v>
       </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="17" t="s">
+      <x:c r="B15" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="20" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="s"/>
-      <x:c r="D15" s="18" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="19" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="22" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -10624,20 +10604,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10660,162 +10640,162 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>45979.0549779514</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46006.269013287</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="H9" s="32">
+        <x:v>45972.2314280556</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>45979.0549779514</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="K9" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="33">
-        <x:v>46006.269013287</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
-        <x:v>45972.2314280556</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L9" s="33">
+      <x:c r="L9" s="34">
         <x:v>45992.0065612963</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -11917,20 +11897,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11953,298 +11933,298 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>46031.0429770602</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46043.2977226505</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="H9" s="32">
+        <x:v>46029.1168153009</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="K9" s="33" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46036.0526802894</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>46031.0429770602</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L8" s="33">
-        <x:v>46043.2977226505</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="G10" s="30" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
+      <x:c r="H10" s="32">
+        <x:v>46029.1129715509</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="s">
+      <x:c r="K10" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>46036.0583638426</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="G9" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="H9" s="31">
-        <x:v>46029.1168153009</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
+      <x:c r="F11" s="30" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L9" s="33">
-        <x:v>46036.0526802894</x:v>
-      </x:c>
-      <x:c r="M9" s="29" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>163</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
+      <x:c r="H11" s="32">
+        <x:v>46036.9292262963</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="K11" s="33" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>46050.0472434028</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>46029.1129715509</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="F12" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46034.174115162</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="K12" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46036.0583638426</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>163</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>46036.9292262963</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46050.0472434028</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>46034.174115162</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
+      <x:c r="L12" s="34">
         <x:v>46044.2691750116</x:v>
       </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="17" t="s">
+      <x:c r="B15" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="20" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="s"/>
-      <x:c r="D15" s="18" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="19" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="22" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -13343,20 +13323,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13379,298 +13359,298 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>46072.0406637037</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46077.082186713</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46078.028276956</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="H9" s="32">
+        <x:v>46050.1475945255</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
+      <x:c r="K9" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46057.9737815278</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="H8" s="31">
-        <x:v>46072.0406637037</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>46077.082186713</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="F10" s="30" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46057.2343839583</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>46072.0668155208</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46066.1502727199</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="33">
-        <x:v>46078.028276956</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
-        <x:v>46050.1475945255</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L9" s="33">
-        <x:v>46057.9737815278</x:v>
-      </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
+      <x:c r="L11" s="34">
+        <x:v>46077.954281088</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>46057.2343839583</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
+      <x:c r="F12" s="30" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46072.0668155208</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="G12" s="30" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46051.2882746759</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>44445</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>46066.1502727199</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46077.954281088</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>46051.2882746759</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>44445</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
+      <x:c r="K12" s="33" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L12" s="33">
+      <x:c r="L12" s="34">
         <x:v>46057.9635980093</x:v>
       </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="17" t="s">
+      <x:c r="B15" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="20" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="s"/>
-      <x:c r="D15" s="18" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="19" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="22" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -15,6 +15,7 @@
     <x:sheet name="January 2026" sheetId="13" r:id="rId13"/>
     <x:sheet name="February 2026" sheetId="14" r:id="rId14"/>
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
+    <x:sheet name="April 2026" sheetId="16" r:id="rId16"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="280">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="285">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -870,6 +871,21 @@
   </x:si>
   <x:si>
     <x:t>1216192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOHNRIN ROSALIJOS GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 purok santan, bomba, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21-SROPIX-13838</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1432-568</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216229</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3484,6 +3500,1275 @@
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46107.1249875579</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45842</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>46126.1994933218</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -897,7 +897,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -937,14 +937,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1224,7 +1216,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1235,16 +1227,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1256,65 +1245,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1349,99 +1338,95 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1743,17 +1728,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1776,754 +1761,754 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46062.3800913889</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46104.0851025694</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46065.3312544444</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45700</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46084.1560858449</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46085.2764846181</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>44879</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>1290</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46093.2000157407</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46065.2288648495</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46084.1582202315</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46085.3008007755</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>46386</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46093.2151637732</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>46085.2858432523</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>46096</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>46093.2057128819</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="30" t="s">
+      <x:c r="B14" s="29" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="C14" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H14" s="32">
+      <x:c r="H14" s="31">
         <x:v>46072.3153026736</x:v>
       </x:c>
-      <x:c r="I14" s="32">
+      <x:c r="I14" s="31">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="K14" s="33" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L14" s="34">
+      <x:c r="L14" s="33">
         <x:v>46090.3114235417</x:v>
       </x:c>
-      <x:c r="M14" s="30" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="30" t="s">
+      <x:c r="B15" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="C15" s="29" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="H15" s="32">
+      <x:c r="H15" s="31">
         <x:v>46073.0262962616</x:v>
       </x:c>
-      <x:c r="I15" s="32">
+      <x:c r="I15" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="K15" s="33" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L15" s="34">
+      <x:c r="L15" s="33">
         <x:v>46090.2670310069</x:v>
       </x:c>
-      <x:c r="M15" s="30" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="30" t="s">
+      <x:c r="B16" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s">
+      <x:c r="C16" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s">
+      <x:c r="D16" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="E16" s="29" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="G16" s="29" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H16" s="32">
+      <x:c r="H16" s="31">
         <x:v>46077.2103691435</x:v>
       </x:c>
-      <x:c r="I16" s="32">
+      <x:c r="I16" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J16" s="31" t="s">
+      <x:c r="J16" s="30" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="K16" s="33" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="34">
+      <x:c r="L16" s="33">
         <x:v>46090.253629537</x:v>
       </x:c>
-      <x:c r="M16" s="30" t="s">
+      <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="30" t="s">
+      <x:c r="B17" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s">
+      <x:c r="C17" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
+      <x:c r="D17" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="E17" s="29" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="F17" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="G17" s="29" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H17" s="32">
+      <x:c r="H17" s="31">
         <x:v>46073.0478536458</x:v>
       </x:c>
-      <x:c r="I17" s="32">
+      <x:c r="I17" s="31">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J17" s="31" t="s">
+      <x:c r="J17" s="30" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="K17" s="33" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L17" s="34">
+      <x:c r="L17" s="33">
         <x:v>46090.2431909954</x:v>
       </x:c>
-      <x:c r="M17" s="30" t="s">
+      <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s">
+      <x:c r="C18" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D18" s="31" t="s">
+      <x:c r="D18" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="30" t="s">
+      <x:c r="E18" s="29" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F18" s="30" t="s">
+      <x:c r="F18" s="29" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="G18" s="29" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H18" s="32">
+      <x:c r="H18" s="31">
         <x:v>46073.10951125</x:v>
       </x:c>
-      <x:c r="I18" s="32">
+      <x:c r="I18" s="31">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J18" s="31" t="s">
+      <x:c r="J18" s="30" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K18" s="33" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L18" s="34">
+      <x:c r="L18" s="33">
         <x:v>46091.1210900116</x:v>
       </x:c>
-      <x:c r="M18" s="30" t="s">
+      <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="30" t="s">
+      <x:c r="B19" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s">
+      <x:c r="C19" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="D19" s="31" t="s">
+      <x:c r="D19" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="30" t="s">
+      <x:c r="E19" s="29" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F19" s="30" t="s">
+      <x:c r="F19" s="29" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="G19" s="29" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="H19" s="32">
+      <x:c r="H19" s="31">
         <x:v>46073.0611031366</x:v>
       </x:c>
-      <x:c r="I19" s="32">
+      <x:c r="I19" s="31">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J19" s="31" t="s">
+      <x:c r="J19" s="30" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="K19" s="33" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L19" s="34">
+      <x:c r="L19" s="33">
         <x:v>46090.2266513079</x:v>
       </x:c>
-      <x:c r="M19" s="30" t="s">
+      <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="30" t="s">
+      <x:c r="B20" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s">
+      <x:c r="C20" s="29" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="D20" s="31" t="s">
+      <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="30" t="s">
+      <x:c r="E20" s="29" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="F20" s="30" t="s">
+      <x:c r="F20" s="29" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="G20" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="H20" s="32">
+      <x:c r="H20" s="31">
         <x:v>46077.2683575231</x:v>
       </x:c>
-      <x:c r="I20" s="32">
+      <x:c r="I20" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J20" s="31" t="s">
+      <x:c r="J20" s="30" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="K20" s="33" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L20" s="34">
+      <x:c r="L20" s="33">
         <x:v>46090.2806125347</x:v>
       </x:c>
-      <x:c r="M20" s="30" t="s">
+      <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="30" t="s">
+      <x:c r="B21" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s">
+      <x:c r="C21" s="29" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="D21" s="31" t="s">
+      <x:c r="D21" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="30" t="s">
+      <x:c r="E21" s="29" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F21" s="30" t="s">
+      <x:c r="F21" s="29" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="G21" s="29" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="H21" s="32">
+      <x:c r="H21" s="31">
         <x:v>46073.0763545833</x:v>
       </x:c>
-      <x:c r="I21" s="32">
+      <x:c r="I21" s="31">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J21" s="31" t="s">
+      <x:c r="J21" s="30" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="K21" s="33" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L21" s="34">
+      <x:c r="L21" s="33">
         <x:v>46090.2162962268</x:v>
       </x:c>
-      <x:c r="M21" s="30" t="s">
+      <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="30" t="s">
+      <x:c r="B22" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s">
+      <x:c r="C22" s="29" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="D22" s="31" t="s">
+      <x:c r="D22" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="30" t="s">
+      <x:c r="E22" s="29" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="s">
+      <x:c r="F22" s="29" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="G22" s="29" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="H22" s="32">
+      <x:c r="H22" s="31">
         <x:v>46077.1834319213</x:v>
       </x:c>
-      <x:c r="I22" s="32">
+      <x:c r="I22" s="31">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J22" s="31" t="s">
+      <x:c r="J22" s="30" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="K22" s="33" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L22" s="34">
+      <x:c r="L22" s="33">
         <x:v>46091.2388780324</x:v>
       </x:c>
-      <x:c r="M22" s="30" t="s">
+      <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="30" t="s">
+      <x:c r="B23" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s">
+      <x:c r="C23" s="29" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="D23" s="31" t="s">
+      <x:c r="D23" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="30" t="s">
+      <x:c r="E23" s="29" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="F23" s="30" t="s">
+      <x:c r="F23" s="29" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="G23" s="29" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="H23" s="32">
+      <x:c r="H23" s="31">
         <x:v>46071.2853697569</x:v>
       </x:c>
-      <x:c r="I23" s="32">
+      <x:c r="I23" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J23" s="31" t="s">
+      <x:c r="J23" s="30" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="K23" s="33" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L23" s="34">
+      <x:c r="L23" s="33">
         <x:v>46094.1777229282</x:v>
       </x:c>
-      <x:c r="M23" s="30" t="s">
+      <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="30" t="s">
+      <x:c r="B24" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s">
+      <x:c r="C24" s="29" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="s">
+      <x:c r="D24" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="30" t="s">
+      <x:c r="E24" s="29" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="F24" s="30" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="H24" s="32">
+      <x:c r="H24" s="31">
         <x:v>46090.3681394907</x:v>
       </x:c>
-      <x:c r="I24" s="32">
+      <x:c r="I24" s="31">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J24" s="31" t="s">
+      <x:c r="J24" s="30" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="K24" s="33" t="n">
+      <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L24" s="34">
+      <x:c r="L24" s="33">
         <x:v>46094.1826630093</x:v>
       </x:c>
-      <x:c r="M24" s="30" t="s">
+      <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="18" t="s">
+      <x:c r="B27" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C27" s="19" t="s"/>
-      <x:c r="D27" s="19" t="s"/>
-      <x:c r="E27" s="20" t="s"/>
-      <x:c r="F27" s="20" t="s"/>
+      <x:c r="C27" s="18" t="s"/>
+      <x:c r="D27" s="18" t="s"/>
+      <x:c r="E27" s="19" t="s"/>
+      <x:c r="F27" s="19" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="21" t="s">
+      <x:c r="B28" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="23" t="s">
+      <x:c r="C28" s="21" t="s"/>
+      <x:c r="D28" s="21" t="s"/>
+      <x:c r="E28" s="21" t="s"/>
+      <x:c r="F28" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="24" t="s">
+      <x:c r="B29" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
+      <x:c r="C29" s="24" t="s"/>
+      <x:c r="D29" s="24" t="s"/>
+      <x:c r="E29" s="24" t="s"/>
+      <x:c r="F29" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="24" t="s">
+      <x:c r="B30" s="23" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C30" s="25" t="s"/>
-      <x:c r="D30" s="25" t="s"/>
-      <x:c r="E30" s="25" t="s"/>
-      <x:c r="F30" s="26" t="n">
+      <x:c r="C30" s="24" t="s"/>
+      <x:c r="D30" s="24" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="24" t="s">
+      <x:c r="B31" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="s"/>
-      <x:c r="D31" s="25" t="s"/>
-      <x:c r="E31" s="25" t="s"/>
-      <x:c r="F31" s="26" t="n">
+      <x:c r="C31" s="24" t="s"/>
+      <x:c r="D31" s="24" t="s"/>
+      <x:c r="E31" s="24" t="s"/>
+      <x:c r="F31" s="25" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="27" t="s">
+      <x:c r="B32" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3613,17 +3598,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3646,80 +3631,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>46107.1249875579</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>45842</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>46126.1994933218</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3739,44 +3724,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4882,17 +4867,17 @@
       <x:c r="B5" s="12">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4915,80 +4900,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>45861.1810907407</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>45862.1344605671</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -5008,44 +4993,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6151,17 +6136,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6184,434 +6169,434 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>45881.1074470139</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>45889</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>45882.1141826157</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>45881.2688653125</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>45882.0237933565</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>45897.2409947801</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>45681</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>45897.2777466898</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>45875.2668430556</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>45875.2668525</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>45877.2327351852</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>45889.2616895949</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>45889.2616989468</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>45891.1583043171</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>45889.1521108681</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>44272</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>45891.1532978241</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="30" t="s">
+      <x:c r="B14" s="29" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="C14" s="29" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H14" s="32">
+      <x:c r="H14" s="31">
         <x:v>45887.5499379745</x:v>
       </x:c>
-      <x:c r="I14" s="32">
+      <x:c r="I14" s="31">
         <x:v>45887.5499545023</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="K14" s="33" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L14" s="34">
+      <x:c r="L14" s="33">
         <x:v>45891.1027280787</x:v>
       </x:c>
-      <x:c r="M14" s="30" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="30" t="s">
+      <x:c r="B15" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="C15" s="29" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H15" s="32">
+      <x:c r="H15" s="31">
         <x:v>45883.2595720718</x:v>
       </x:c>
-      <x:c r="I15" s="32">
+      <x:c r="I15" s="31">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="K15" s="33" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="34">
+      <x:c r="L15" s="33">
         <x:v>45883.2880279051</x:v>
       </x:c>
-      <x:c r="M15" s="30" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="18" t="s">
+      <x:c r="B18" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C18" s="19" t="s"/>
-      <x:c r="D18" s="19" t="s"/>
-      <x:c r="E18" s="20" t="s"/>
-      <x:c r="F18" s="20" t="s"/>
+      <x:c r="C18" s="18" t="s"/>
+      <x:c r="D18" s="18" t="s"/>
+      <x:c r="E18" s="19" t="s"/>
+      <x:c r="F18" s="19" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="B19" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="s">
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+      <x:c r="B20" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="24" t="s">
+      <x:c r="B21" s="23" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="n">
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+      <x:c r="B22" s="23" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="n">
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="24" t="s"/>
+      <x:c r="F22" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+      <x:c r="B23" s="23" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="C23" s="24" t="s"/>
+      <x:c r="D23" s="24" t="s"/>
+      <x:c r="E23" s="24" t="s"/>
+      <x:c r="F23" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="24" t="s">
+      <x:c r="B24" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="n">
+      <x:c r="C24" s="24" t="s"/>
+      <x:c r="D24" s="24" t="s"/>
+      <x:c r="E24" s="24" t="s"/>
+      <x:c r="F24" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="27" t="s">
+      <x:c r="B25" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="n">
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -7710,17 +7695,17 @@
       <x:c r="B5" s="12">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7743,336 +7728,336 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>45902.1777587269</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>45781</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>45911.9486641782</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>45887.291765787</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>45903.117765081</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>45911.4396314699</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>45911.4396406018</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>45918.0952106019</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>45925.397251713</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>47021</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>45930.1169604282</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>45916.1769203588</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>45930.1671706366</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>45912.4737565972</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>45918.0905875926</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="18" t="s">
+      <x:c r="B16" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="20" t="s"/>
-      <x:c r="F16" s="20" t="s"/>
+      <x:c r="C16" s="18" t="s"/>
+      <x:c r="D16" s="18" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="19" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="B17" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="s">
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+      <x:c r="B18" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="24" t="s">
+      <x:c r="B19" s="23" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+      <x:c r="B20" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="27" t="s">
+      <x:c r="B21" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -9173,17 +9158,17 @@
       <x:c r="B5" s="12">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9206,173 +9191,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>45938.0053813889</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>45945.1196250694</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>45945.2727709838</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>45953.1511070255</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+      <x:c r="B12" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+      <x:c r="B14" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -10477,17 +10462,17 @@
       <x:c r="B5" s="12">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10510,287 +10495,287 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>45944.1129354167</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>45971.3164108796</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>45954.1265640162</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45626</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>45967.0018301736</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>45965.2541525</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>45971.1502294097</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>45966.1203235417</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>45975.3046220602</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>45966.1218093634</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>45975.3123537269</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="18" t="s">
+      <x:c r="B15" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="20" t="s"/>
+      <x:c r="C15" s="18" t="s"/>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="19" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+      <x:c r="B18" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="27" t="s">
+      <x:c r="B19" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -11892,17 +11877,17 @@
       <x:c r="B5" s="12">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11925,162 +11910,162 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>45979.0549779514</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46006.269013287</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>45972.2314280556</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>45992.0065612963</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+      <x:c r="B12" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+      <x:c r="B14" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="B15" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -13185,17 +13170,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13218,298 +13203,298 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46031.0429770602</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46015</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46043.2977226505</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46029.1168153009</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46036.0526802894</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46029.1129715509</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46036.0583638426</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46036.9292262963</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46050.0472434028</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46034.174115162</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46044.2691750116</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="18" t="s">
+      <x:c r="B15" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="20" t="s"/>
+      <x:c r="C15" s="18" t="s"/>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="19" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+      <x:c r="B18" s="23" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="24" t="s">
+      <x:c r="B19" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="27" t="s">
+      <x:c r="B20" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -14611,17 +14596,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -14644,298 +14629,298 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46072.0406637037</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46077.082186713</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46078.028276956</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46050.1475945255</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>45988</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46057.9737815278</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46057.2343839583</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46072.0668155208</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46066.1502727199</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46077.954281088</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46051.2882746759</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46057.9635980093</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="18" t="s">
+      <x:c r="B15" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="20" t="s"/>
+      <x:c r="C15" s="18" t="s"/>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="19" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="23" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+      <x:c r="B18" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="24" t="s">
+      <x:c r="B19" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="27" t="s">
+      <x:c r="B20" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
